--- a/figs/data/fig14_lines.xlsx
+++ b/figs/data/fig14_lines.xlsx
@@ -189,7 +189,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'OLTP→Varmail'!C1</f>
+              <f>'OLTP→Varmail'!D1</f>
             </strRef>
           </tx>
           <spPr>
@@ -210,12 +210,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'OLTP→Varmail'!$A$2:$A$62</f>
+              <f>'OLTP→Varmail'!$C$2:$C$62</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'OLTP→Varmail'!$C$2:$C$62</f>
+              <f>'OLTP→Varmail'!$D$2:$D$62</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -225,7 +225,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'OLTP→Varmail'!D1</f>
+              <f>'OLTP→Varmail'!F1</f>
             </strRef>
           </tx>
           <spPr>
@@ -246,12 +246,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'OLTP→Varmail'!$A$2:$A$62</f>
+              <f>'OLTP→Varmail'!$E$2:$E$62</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'OLTP→Varmail'!$D$2:$D$62</f>
+              <f>'OLTP→Varmail'!$F$2:$F$62</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -261,7 +261,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'OLTP→Varmail'!E1</f>
+              <f>'OLTP→Varmail'!H1</f>
             </strRef>
           </tx>
           <spPr>
@@ -282,12 +282,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'OLTP→Varmail'!$A$2:$A$62</f>
+              <f>'OLTP→Varmail'!$G$2:$G$62</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'OLTP→Varmail'!$E$2:$E$62</f>
+              <f>'OLTP→Varmail'!$H$2:$H$62</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -421,7 +421,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'FIO-Fast→Varmail'!C1</f>
+              <f>'FIO-Fast→Varmail'!D1</f>
             </strRef>
           </tx>
           <spPr>
@@ -442,12 +442,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'FIO-Fast→Varmail'!$A$2:$A$90</f>
+              <f>'FIO-Fast→Varmail'!$C$2:$C$90</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'FIO-Fast→Varmail'!$C$2:$C$90</f>
+              <f>'FIO-Fast→Varmail'!$D$2:$D$90</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -457,7 +457,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'FIO-Fast→Varmail'!D1</f>
+              <f>'FIO-Fast→Varmail'!F1</f>
             </strRef>
           </tx>
           <spPr>
@@ -478,12 +478,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'FIO-Fast→Varmail'!$A$2:$A$90</f>
+              <f>'FIO-Fast→Varmail'!$E$2:$E$90</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'FIO-Fast→Varmail'!$D$2:$D$90</f>
+              <f>'FIO-Fast→Varmail'!$F$2:$F$90</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -493,7 +493,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'FIO-Fast→Varmail'!E1</f>
+              <f>'FIO-Fast→Varmail'!H1</f>
             </strRef>
           </tx>
           <spPr>
@@ -514,12 +514,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'FIO-Fast→Varmail'!$A$2:$A$90</f>
+              <f>'FIO-Fast→Varmail'!$G$2:$G$90</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'FIO-Fast→Varmail'!$E$2:$E$90</f>
+              <f>'FIO-Fast→Varmail'!$H$2:$H$90</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -638,12 +638,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'YCSB-A→YCSB-B'!$A$2:$A$41</f>
+              <f>'YCSB-A→YCSB-B'!$A$2:$A$40</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'YCSB-A→YCSB-B'!$B$2:$B$41</f>
+              <f>'YCSB-A→YCSB-B'!$B$2:$B$40</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -653,7 +653,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'YCSB-A→YCSB-B'!C1</f>
+              <f>'YCSB-A→YCSB-B'!D1</f>
             </strRef>
           </tx>
           <spPr>
@@ -674,12 +674,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'YCSB-A→YCSB-B'!$A$2:$A$41</f>
+              <f>'YCSB-A→YCSB-B'!$C$2:$C$40</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'YCSB-A→YCSB-B'!$C$2:$C$41</f>
+              <f>'YCSB-A→YCSB-B'!$D$2:$D$40</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -689,7 +689,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'YCSB-A→YCSB-B'!D1</f>
+              <f>'YCSB-A→YCSB-B'!F1</f>
             </strRef>
           </tx>
           <spPr>
@@ -710,12 +710,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'YCSB-A→YCSB-B'!$A$2:$A$41</f>
+              <f>'YCSB-A→YCSB-B'!$E$2:$E$40</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'YCSB-A→YCSB-B'!$D$2:$D$41</f>
+              <f>'YCSB-A→YCSB-B'!$F$2:$F$40</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -725,7 +725,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'YCSB-A→YCSB-B'!E1</f>
+              <f>'YCSB-A→YCSB-B'!H1</f>
             </strRef>
           </tx>
           <spPr>
@@ -746,12 +746,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'YCSB-A→YCSB-B'!$A$2:$A$41</f>
+              <f>'YCSB-A→YCSB-B'!$G$2:$G$40</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'YCSB-A→YCSB-B'!$E$2:$E$41</f>
+              <f>'YCSB-A→YCSB-B'!$H$2:$H$40</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -885,7 +885,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'YCSB-A→OLTP'!C1</f>
+              <f>'YCSB-A→OLTP'!D1</f>
             </strRef>
           </tx>
           <spPr>
@@ -906,12 +906,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'YCSB-A→OLTP'!$A$2:$A$39</f>
+              <f>'YCSB-A→OLTP'!$C$2:$C$39</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'YCSB-A→OLTP'!$C$2:$C$39</f>
+              <f>'YCSB-A→OLTP'!$D$2:$D$39</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -921,7 +921,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'YCSB-A→OLTP'!D1</f>
+              <f>'YCSB-A→OLTP'!F1</f>
             </strRef>
           </tx>
           <spPr>
@@ -942,12 +942,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'YCSB-A→OLTP'!$A$2:$A$39</f>
+              <f>'YCSB-A→OLTP'!$E$2:$E$39</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'YCSB-A→OLTP'!$D$2:$D$39</f>
+              <f>'YCSB-A→OLTP'!$F$2:$F$39</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -957,7 +957,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'YCSB-A→OLTP'!E1</f>
+              <f>'YCSB-A→OLTP'!H1</f>
             </strRef>
           </tx>
           <spPr>
@@ -978,12 +978,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'YCSB-A→OLTP'!$A$2:$A$39</f>
+              <f>'YCSB-A→OLTP'!$G$2:$G$39</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'YCSB-A→OLTP'!$E$2:$E$39</f>
+              <f>'YCSB-A→OLTP'!$H$2:$H$39</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -1059,7 +1059,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1086,7 +1086,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1113,7 +1113,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1140,7 +1140,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1452,36 +1452,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>경과(분)</t>
+          <t>iCAT-v4 시간(분)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>iCAT-v4</t>
+          <t>iCAT-v4 WAF</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>CAT-47 (최적)</t>
+          <t>CAT-47 (최적) 시간(분)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>CAT-50 (견고)</t>
+          <t>CAT-47 (최적) WAF</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>CAT-37 (기본)</t>
+          <t>CAT-50 (견고) 시간(분)</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CAT-50 (견고) WAF</t>
+        </is>
+      </c>
       <c r="G1" t="inlineStr">
+        <is>
+          <t>CAT-37 (기본) 시간(분)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>CAT-37 (기본) WAF</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>워크로드 전환 시점(분)</t>
         </is>
@@ -1495,15 +1510,24 @@
         <v>1.5101</v>
       </c>
       <c r="C2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D2" t="n">
         <v>1.4927</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F2" t="n">
         <v>1.4228</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2" t="n">
         <v>1.5039</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>iCAT-v4: 16.0</t>
         </is>
@@ -1517,15 +1541,24 @@
         <v>1.4726</v>
       </c>
       <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
         <v>1.2847</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
         <v>1.252</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
         <v>1.3942</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>CAT-47 (최적): 15.6</t>
         </is>
@@ -1539,15 +1572,24 @@
         <v>1.2936</v>
       </c>
       <c r="C4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D4" t="n">
         <v>1.2792</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F4" t="n">
         <v>1.2599</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H4" t="n">
         <v>1.3698</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>CAT-50 (견고): 15.5</t>
         </is>
@@ -1561,15 +1603,24 @@
         <v>1.2703</v>
       </c>
       <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
         <v>1.2729</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
         <v>1.2642</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
         <v>1.3353</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>CAT-37 (기본): 15.1</t>
         </is>
@@ -1583,12 +1634,21 @@
         <v>1.2833</v>
       </c>
       <c r="C6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D6" t="n">
         <v>1.2695</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F6" t="n">
         <v>1.2519</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H6" t="n">
         <v>1.342</v>
       </c>
     </row>
@@ -1600,12 +1660,21 @@
         <v>1.2615</v>
       </c>
       <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
         <v>1.262</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
         <v>1.2544</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
         <v>1.3496</v>
       </c>
     </row>
@@ -1617,12 +1686,21 @@
         <v>1.2686</v>
       </c>
       <c r="C8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D8" t="n">
         <v>1.2576</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F8" t="n">
         <v>1.2446</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H8" t="n">
         <v>1.3366</v>
       </c>
     </row>
@@ -1634,12 +1712,21 @@
         <v>1.2591</v>
       </c>
       <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
         <v>1.2588</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
         <v>1.2382</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
         <v>1.337</v>
       </c>
     </row>
@@ -1651,12 +1738,21 @@
         <v>1.2641</v>
       </c>
       <c r="C10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D10" t="n">
         <v>1.2579</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F10" t="n">
         <v>1.2398</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="H10" t="n">
         <v>1.3359</v>
       </c>
     </row>
@@ -1668,12 +1764,21 @@
         <v>1.2644</v>
       </c>
       <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
         <v>1.2569</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
         <v>1.2383</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="H11" t="n">
         <v>1.3295</v>
       </c>
     </row>
@@ -1685,12 +1790,21 @@
         <v>1.2673</v>
       </c>
       <c r="C12" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="D12" t="n">
         <v>1.2562</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F12" t="n">
         <v>1.2447</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="H12" t="n">
         <v>1.3298</v>
       </c>
     </row>
@@ -1702,12 +1816,21 @@
         <v>1.2641</v>
       </c>
       <c r="C13" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="D13" t="n">
         <v>1.2555</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" t="n">
         <v>1.2351</v>
       </c>
-      <c r="E13" t="n">
+      <c r="G13" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="H13" t="n">
         <v>1.3327</v>
       </c>
     </row>
@@ -1719,12 +1842,21 @@
         <v>1.2517</v>
       </c>
       <c r="C14" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="D14" t="n">
         <v>1.2539</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F14" t="n">
         <v>1.2379</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="H14" t="n">
         <v>1.3259</v>
       </c>
     </row>
@@ -1736,12 +1868,21 @@
         <v>1.2816</v>
       </c>
       <c r="C15" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="D15" t="n">
         <v>1.2555</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" t="n">
         <v>1.2358</v>
       </c>
-      <c r="E15" t="n">
+      <c r="G15" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="H15" t="n">
         <v>1.3205</v>
       </c>
     </row>
@@ -1753,12 +1894,21 @@
         <v>1.2358</v>
       </c>
       <c r="C16" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="D16" t="n">
         <v>1.2534</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F16" t="n">
         <v>1.2344</v>
       </c>
-      <c r="E16" t="n">
+      <c r="G16" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="H16" t="n">
         <v>1.3235</v>
       </c>
     </row>
@@ -1770,757 +1920,1159 @@
         <v>1.2585</v>
       </c>
       <c r="C17" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="D17" t="n">
         <v>1.2546</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" t="n">
         <v>1.2365</v>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="H17" t="n">
         <v>1.321</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>8.5</v>
+        <v>8.52</v>
       </c>
       <c r="B18" t="n">
         <v>1.2297</v>
       </c>
       <c r="C18" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="D18" t="n">
         <v>1.2561</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F18" t="n">
         <v>1.2387</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="H18" t="n">
         <v>1.3205</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>9</v>
+        <v>9.02</v>
       </c>
       <c r="B19" t="n">
         <v>1.2333</v>
       </c>
       <c r="C19" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D19" t="n">
         <v>1.255</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
+        <v>9</v>
+      </c>
+      <c r="F19" t="n">
         <v>1.2386</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="H19" t="n">
         <v>1.3189</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>9.5</v>
+        <v>9.52</v>
       </c>
       <c r="B20" t="n">
         <v>1.2266</v>
       </c>
       <c r="C20" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="D20" t="n">
         <v>1.252</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="F20" t="n">
         <v>1.2353</v>
       </c>
-      <c r="E20" t="n">
+      <c r="G20" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="H20" t="n">
         <v>1.3187</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>10</v>
+        <v>10.02</v>
       </c>
       <c r="B21" t="n">
         <v>1.2277</v>
       </c>
       <c r="C21" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="D21" t="n">
         <v>1.2546</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="F21" t="n">
         <v>1.2363</v>
       </c>
-      <c r="E21" t="n">
+      <c r="G21" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="H21" t="n">
         <v>1.3128</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>10.5</v>
+        <v>10.52</v>
       </c>
       <c r="B22" t="n">
         <v>1.2255</v>
       </c>
-      <c r="D22" t="n">
+      <c r="C22" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="F22" t="n">
         <v>1.2377</v>
       </c>
-      <c r="E22" t="n">
+      <c r="G22" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="H22" t="n">
         <v>1.3155</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>11</v>
+        <v>11.02</v>
       </c>
       <c r="B23" t="n">
         <v>1.2259</v>
       </c>
       <c r="C23" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.2529</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="F23" t="n">
         <v>1.2403</v>
       </c>
-      <c r="E23" t="n">
+      <c r="G23" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="H23" t="n">
         <v>1.3125</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>11.5</v>
+        <v>11.52</v>
       </c>
       <c r="B24" t="n">
         <v>1.226</v>
       </c>
       <c r="C24" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="D24" t="n">
         <v>1.2528</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="F24" t="n">
         <v>1.2405</v>
       </c>
-      <c r="E24" t="n">
+      <c r="G24" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="H24" t="n">
         <v>1.3137</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>12</v>
+        <v>12.02</v>
       </c>
       <c r="B25" t="n">
         <v>1.2334</v>
       </c>
       <c r="C25" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="D25" t="n">
         <v>1.2529</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="F25" t="n">
         <v>1.2409</v>
       </c>
-      <c r="E25" t="n">
+      <c r="G25" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="H25" t="n">
         <v>1.3136</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>12.5</v>
+        <v>12.53</v>
       </c>
       <c r="B26" t="n">
         <v>1.2232</v>
       </c>
       <c r="C26" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="D26" t="n">
         <v>1.2532</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="F26" t="n">
         <v>1.2405</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="H26" t="n">
         <v>1.3123</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>13</v>
+        <v>13.03</v>
       </c>
       <c r="B27" t="n">
         <v>1.2265</v>
       </c>
       <c r="C27" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="D27" t="n">
         <v>1.2523</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="F27" t="n">
         <v>1.2425</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="H27" t="n">
         <v>1.312</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>13.5</v>
+        <v>13.53</v>
       </c>
       <c r="B28" t="n">
         <v>1.2197</v>
       </c>
       <c r="C28" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="D28" t="n">
         <v>1.2525</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
+        <v>13.52</v>
+      </c>
+      <c r="F28" t="n">
         <v>1.242</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="H28" t="n">
         <v>1.3113</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>14</v>
+        <v>14.03</v>
       </c>
       <c r="B29" t="n">
         <v>1.2197</v>
       </c>
       <c r="C29" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="D29" t="n">
         <v>1.2526</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="F29" t="n">
         <v>1.2423</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="H29" t="n">
         <v>1.3101</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>14.5</v>
+        <v>14.53</v>
       </c>
       <c r="B30" t="n">
         <v>1.2198</v>
       </c>
       <c r="C30" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D30" t="n">
         <v>1.2538</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="F30" t="n">
         <v>1.244</v>
       </c>
-      <c r="E30" t="n">
+      <c r="G30" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="H30" t="n">
         <v>1.3111</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>15</v>
+        <v>15.03</v>
       </c>
       <c r="B31" t="n">
         <v>1.2199</v>
       </c>
       <c r="C31" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="D31" t="n">
         <v>1.2515</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="F31" t="n">
         <v>1.2454</v>
       </c>
-      <c r="E31" t="n">
+      <c r="G31" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="H31" t="n">
         <v>1.3606</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>15.5</v>
+        <v>15.53</v>
       </c>
       <c r="C32" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D32" t="n">
         <v>1.6821</v>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="F32" t="n">
         <v>1.5873</v>
       </c>
-      <c r="E32" t="n">
+      <c r="G32" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="H32" t="n">
         <v>2.1374</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>16</v>
+        <v>16.03</v>
       </c>
       <c r="B33" t="n">
         <v>1.5036</v>
       </c>
       <c r="C33" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="D33" t="n">
         <v>1.9809</v>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
+        <v>16.02</v>
+      </c>
+      <c r="F33" t="n">
         <v>2.0166</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="H33" t="n">
         <v>2.3831</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>16.5</v>
+        <v>16.53</v>
       </c>
       <c r="B34" t="n">
         <v>1.9627</v>
       </c>
       <c r="C34" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="D34" t="n">
         <v>2.0074</v>
       </c>
-      <c r="D34" t="n">
+      <c r="E34" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="F34" t="n">
         <v>2.064</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
+        <v>16.55</v>
+      </c>
+      <c r="H34" t="n">
         <v>2.3912</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>17</v>
+        <v>17.03</v>
       </c>
       <c r="B35" t="n">
         <v>1.9591</v>
       </c>
       <c r="C35" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="D35" t="n">
         <v>2.011</v>
       </c>
-      <c r="D35" t="n">
+      <c r="E35" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="F35" t="n">
         <v>2.0791</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="H35" t="n">
         <v>2.3943</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>17.5</v>
+        <v>17.53</v>
       </c>
       <c r="B36" t="n">
         <v>1.9602</v>
       </c>
       <c r="C36" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D36" t="n">
         <v>2.0183</v>
       </c>
-      <c r="D36" t="n">
+      <c r="E36" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="F36" t="n">
         <v>2.0877</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="H36" t="n">
         <v>2.4031</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>18</v>
+        <v>18.03</v>
       </c>
       <c r="B37" t="n">
         <v>1.9649</v>
       </c>
       <c r="C37" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="D37" t="n">
         <v>2.0225</v>
       </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
+        <v>18.02</v>
+      </c>
+      <c r="F37" t="n">
         <v>2.0921</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="H37" t="n">
         <v>2.4016</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>18.5</v>
+        <v>18.53</v>
       </c>
       <c r="B38" t="n">
         <v>1.9705</v>
       </c>
       <c r="C38" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="D38" t="n">
         <v>2.0224</v>
       </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="F38" t="n">
         <v>2.0911</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="H38" t="n">
         <v>2.4026</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>19</v>
+        <v>19.03</v>
       </c>
       <c r="B39" t="n">
         <v>1.9668</v>
       </c>
       <c r="C39" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="D39" t="n">
         <v>2.0231</v>
       </c>
-      <c r="D39" t="n">
+      <c r="E39" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="F39" t="n">
         <v>2.092</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="H39" t="n">
         <v>2.4054</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>19.5</v>
+        <v>19.53</v>
       </c>
       <c r="B40" t="n">
         <v>1.9673</v>
       </c>
       <c r="C40" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="D40" t="n">
         <v>2.0256</v>
       </c>
-      <c r="D40" t="n">
+      <c r="E40" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="F40" t="n">
         <v>2.0954</v>
       </c>
-      <c r="E40" t="n">
+      <c r="G40" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="H40" t="n">
         <v>2.405</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>20</v>
+        <v>20.03</v>
       </c>
       <c r="B41" t="n">
         <v>1.9674</v>
       </c>
       <c r="C41" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="D41" t="n">
         <v>2.0252</v>
       </c>
-      <c r="D41" t="n">
+      <c r="E41" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="F41" t="n">
         <v>2.0912</v>
       </c>
-      <c r="E41" t="n">
+      <c r="G41" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="H41" t="n">
         <v>2.4048</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>20.5</v>
+        <v>20.53</v>
       </c>
       <c r="B42" t="n">
         <v>1.9679</v>
       </c>
       <c r="C42" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="D42" t="n">
         <v>2.0256</v>
       </c>
-      <c r="D42" t="n">
+      <c r="E42" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="F42" t="n">
         <v>2.0949</v>
       </c>
-      <c r="E42" t="n">
+      <c r="G42" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="H42" t="n">
         <v>2.4002</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>21</v>
+        <v>21.03</v>
       </c>
       <c r="B43" t="n">
         <v>1.9695</v>
       </c>
       <c r="C43" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="D43" t="n">
         <v>2.0234</v>
       </c>
-      <c r="D43" t="n">
+      <c r="E43" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="F43" t="n">
         <v>2.0925</v>
       </c>
-      <c r="E43" t="n">
+      <c r="G43" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="H43" t="n">
         <v>2.3995</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>21.5</v>
+        <v>21.53</v>
       </c>
       <c r="B44" t="n">
         <v>1.965</v>
       </c>
       <c r="C44" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="D44" t="n">
         <v>2.0273</v>
       </c>
-      <c r="D44" t="n">
+      <c r="E44" t="n">
+        <v>21.52</v>
+      </c>
+      <c r="F44" t="n">
         <v>2.0908</v>
       </c>
-      <c r="E44" t="n">
+      <c r="G44" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="H44" t="n">
         <v>2.4031</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>22</v>
+        <v>22.03</v>
       </c>
       <c r="B45" t="n">
         <v>1.9669</v>
       </c>
       <c r="C45" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="D45" t="n">
         <v>2.0238</v>
       </c>
-      <c r="D45" t="n">
+      <c r="E45" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="F45" t="n">
         <v>2.0952</v>
       </c>
-      <c r="E45" t="n">
+      <c r="G45" t="n">
+        <v>22.05</v>
+      </c>
+      <c r="H45" t="n">
         <v>2.4055</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>22.5</v>
+        <v>22.53</v>
       </c>
       <c r="B46" t="n">
         <v>1.9661</v>
       </c>
       <c r="C46" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="D46" t="n">
         <v>2.0249</v>
       </c>
-      <c r="D46" t="n">
+      <c r="E46" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="F46" t="n">
         <v>2.0957</v>
       </c>
-      <c r="E46" t="n">
+      <c r="G46" t="n">
+        <v>22.55</v>
+      </c>
+      <c r="H46" t="n">
         <v>2.4029</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>23</v>
+        <v>23.03</v>
       </c>
       <c r="B47" t="n">
         <v>1.9686</v>
       </c>
       <c r="C47" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="D47" t="n">
         <v>2.0285</v>
       </c>
-      <c r="D47" t="n">
+      <c r="E47" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="F47" t="n">
         <v>2.0964</v>
       </c>
-      <c r="E47" t="n">
+      <c r="G47" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="H47" t="n">
         <v>2.3994</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>23.5</v>
+        <v>23.53</v>
       </c>
       <c r="B48" t="n">
         <v>1.9683</v>
       </c>
       <c r="C48" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="D48" t="n">
         <v>2.025</v>
       </c>
-      <c r="D48" t="n">
+      <c r="E48" t="n">
+        <v>23.52</v>
+      </c>
+      <c r="F48" t="n">
         <v>2.0967</v>
       </c>
-      <c r="E48" t="n">
+      <c r="G48" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="H48" t="n">
         <v>2.4022</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>24</v>
+        <v>24.03</v>
       </c>
       <c r="B49" t="n">
         <v>1.969</v>
       </c>
       <c r="C49" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="D49" t="n">
         <v>2.0243</v>
       </c>
-      <c r="D49" t="n">
+      <c r="E49" t="n">
+        <v>24.02</v>
+      </c>
+      <c r="F49" t="n">
         <v>2.0933</v>
       </c>
-      <c r="E49" t="n">
+      <c r="G49" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="H49" t="n">
         <v>2.3991</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>24.5</v>
+        <v>24.53</v>
       </c>
       <c r="B50" t="n">
         <v>1.9731</v>
       </c>
       <c r="C50" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="D50" t="n">
         <v>2.0255</v>
       </c>
-      <c r="D50" t="n">
+      <c r="E50" t="n">
+        <v>24.52</v>
+      </c>
+      <c r="F50" t="n">
         <v>2.0991</v>
       </c>
-      <c r="E50" t="n">
+      <c r="G50" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="H50" t="n">
         <v>2.4022</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>25</v>
+        <v>25.03</v>
       </c>
       <c r="B51" t="n">
         <v>1.967</v>
       </c>
       <c r="C51" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="D51" t="n">
         <v>2.0265</v>
       </c>
-      <c r="D51" t="n">
+      <c r="E51" t="n">
+        <v>25.02</v>
+      </c>
+      <c r="F51" t="n">
         <v>2.0941</v>
       </c>
-      <c r="E51" t="n">
+      <c r="G51" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="H51" t="n">
         <v>2.3952</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>25.5</v>
+        <v>25.53</v>
       </c>
       <c r="B52" t="n">
         <v>1.9673</v>
       </c>
       <c r="C52" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="D52" t="n">
         <v>2.0251</v>
       </c>
-      <c r="D52" t="n">
+      <c r="E52" t="n">
+        <v>25.52</v>
+      </c>
+      <c r="F52" t="n">
         <v>2.0977</v>
       </c>
-      <c r="E52" t="n">
+      <c r="G52" t="n">
+        <v>25.55</v>
+      </c>
+      <c r="H52" t="n">
         <v>2.3941</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>26</v>
+        <v>26.03</v>
       </c>
       <c r="B53" t="n">
         <v>1.9619</v>
       </c>
       <c r="C53" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="D53" t="n">
         <v>2.0261</v>
       </c>
-      <c r="D53" t="n">
+      <c r="E53" t="n">
+        <v>26.02</v>
+      </c>
+      <c r="F53" t="n">
         <v>2.0948</v>
       </c>
-      <c r="E53" t="n">
+      <c r="G53" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="H53" t="n">
         <v>2.393</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>26.5</v>
+        <v>26.53</v>
       </c>
       <c r="B54" t="n">
         <v>1.9612</v>
       </c>
       <c r="C54" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="D54" t="n">
         <v>2.0244</v>
       </c>
-      <c r="D54" t="n">
+      <c r="E54" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="F54" t="n">
         <v>2.0951</v>
       </c>
-      <c r="E54" t="n">
+      <c r="G54" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="H54" t="n">
         <v>2.3941</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>27</v>
+        <v>27.03</v>
       </c>
       <c r="B55" t="n">
         <v>1.9649</v>
       </c>
       <c r="C55" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="D55" t="n">
         <v>2.0275</v>
       </c>
-      <c r="D55" t="n">
+      <c r="E55" t="n">
+        <v>27.02</v>
+      </c>
+      <c r="F55" t="n">
         <v>2.1033</v>
       </c>
-      <c r="E55" t="n">
+      <c r="G55" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="H55" t="n">
         <v>2.3876</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>27.5</v>
+        <v>27.53</v>
       </c>
       <c r="B56" t="n">
         <v>1.9664</v>
       </c>
       <c r="C56" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="D56" t="n">
         <v>2.0265</v>
       </c>
-      <c r="D56" t="n">
+      <c r="E56" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="F56" t="n">
         <v>2.1016</v>
       </c>
-      <c r="E56" t="n">
+      <c r="G56" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="H56" t="n">
         <v>2.3897</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>28</v>
+        <v>28.03</v>
       </c>
       <c r="B57" t="n">
         <v>1.9675</v>
       </c>
       <c r="C57" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="D57" t="n">
         <v>2.026</v>
       </c>
-      <c r="D57" t="n">
+      <c r="E57" t="n">
+        <v>28.02</v>
+      </c>
+      <c r="F57" t="n">
         <v>2.0993</v>
       </c>
-      <c r="E57" t="n">
+      <c r="G57" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="H57" t="n">
         <v>2.3909</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>28.5</v>
+        <v>28.53</v>
       </c>
       <c r="B58" t="n">
         <v>1.9603</v>
       </c>
       <c r="C58" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="D58" t="n">
         <v>2.0228</v>
       </c>
-      <c r="D58" t="n">
+      <c r="E58" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="F58" t="n">
         <v>2.0936</v>
       </c>
-      <c r="E58" t="n">
+      <c r="G58" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="H58" t="n">
         <v>2.3889</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>29</v>
+        <v>29.03</v>
       </c>
       <c r="B59" t="n">
         <v>1.9619</v>
       </c>
       <c r="C59" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="D59" t="n">
         <v>2.0245</v>
       </c>
-      <c r="D59" t="n">
+      <c r="E59" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="F59" t="n">
         <v>2.0977</v>
       </c>
-      <c r="E59" t="n">
+      <c r="G59" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="H59" t="n">
         <v>2.3873</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>29.5</v>
+        <v>29.53</v>
       </c>
       <c r="B60" t="n">
         <v>1.9601</v>
       </c>
       <c r="C60" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="D60" t="n">
         <v>2.024</v>
       </c>
-      <c r="D60" t="n">
+      <c r="E60" t="n">
+        <v>29.52</v>
+      </c>
+      <c r="F60" t="n">
         <v>2.0965</v>
       </c>
-      <c r="E60" t="n">
+      <c r="G60" t="n">
+        <v>29.55</v>
+      </c>
+      <c r="H60" t="n">
         <v>2.3866</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>30</v>
+        <v>30.03</v>
       </c>
       <c r="B61" t="n">
         <v>1.9615</v>
       </c>
       <c r="C61" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="D61" t="n">
         <v>2.026</v>
       </c>
-      <c r="D61" t="n">
+      <c r="E61" t="n">
+        <v>30.02</v>
+      </c>
+      <c r="F61" t="n">
         <v>2.0966</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>30.5</v>
+        <v>30.53</v>
       </c>
       <c r="B62" t="n">
         <v>1.9625</v>
@@ -2538,36 +3090,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>경과(분)</t>
+          <t>iCAT-v4 시간(분)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>iCAT-v4</t>
+          <t>iCAT-v4 WAF</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>CAT-47 (최적)</t>
+          <t>CAT-47 (최적) 시간(분)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>CAT-50 (견고)</t>
+          <t>CAT-47 (최적) WAF</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>CAT-37 (기본)</t>
+          <t>CAT-50 (견고) 시간(분)</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CAT-50 (견고) WAF</t>
+        </is>
+      </c>
       <c r="G1" t="inlineStr">
+        <is>
+          <t>CAT-37 (기본) 시간(분)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>CAT-37 (기본) WAF</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>워크로드 전환 시점(분)</t>
         </is>
@@ -2581,15 +3148,24 @@
         <v>1.9941</v>
       </c>
       <c r="C2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D2" t="n">
         <v>1.8688</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F2" t="n">
         <v>1.8786</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2" t="n">
         <v>1.93</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>iCAT-v4: 30.0</t>
         </is>
@@ -2603,15 +3179,24 @@
         <v>1.8571</v>
       </c>
       <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
         <v>1.7957</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
         <v>1.7846</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
         <v>1.9474</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>CAT-47 (최적): 30.0</t>
         </is>
@@ -2625,15 +3210,24 @@
         <v>1.8563</v>
       </c>
       <c r="C4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D4" t="n">
         <v>1.855</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F4" t="n">
         <v>1.8714</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H4" t="n">
         <v>1.9714</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>CAT-50 (견고): 30.0</t>
         </is>
@@ -2647,15 +3241,24 @@
         <v>2.0366</v>
       </c>
       <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
         <v>1.8321</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
         <v>1.8533</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
         <v>2.0234</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>CAT-37 (기본): 30.0</t>
         </is>
@@ -2669,12 +3272,21 @@
         <v>2.0436</v>
       </c>
       <c r="C6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D6" t="n">
         <v>1.7755</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F6" t="n">
         <v>1.837</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H6" t="n">
         <v>1.9989</v>
       </c>
     </row>
@@ -2686,12 +3298,21 @@
         <v>2.0411</v>
       </c>
       <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
         <v>1.7795</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
         <v>1.8062</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
         <v>1.9691</v>
       </c>
     </row>
@@ -2703,12 +3324,21 @@
         <v>2.1345</v>
       </c>
       <c r="C8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D8" t="n">
         <v>1.7022</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F8" t="n">
         <v>1.7935</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H8" t="n">
         <v>1.961</v>
       </c>
     </row>
@@ -2720,12 +3350,21 @@
         <v>2.1285</v>
       </c>
       <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
         <v>1.7189</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
         <v>1.7624</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
         <v>1.9097</v>
       </c>
     </row>
@@ -2737,12 +3376,21 @@
         <v>2.1094</v>
       </c>
       <c r="C10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D10" t="n">
         <v>1.6562</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F10" t="n">
         <v>1.7501</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H10" t="n">
         <v>1.8989</v>
       </c>
     </row>
@@ -2754,12 +3402,21 @@
         <v>1.8475</v>
       </c>
       <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
         <v>1.7349</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
         <v>1.7748</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="n">
         <v>1.902</v>
       </c>
     </row>
@@ -2771,12 +3428,21 @@
         <v>1.7646</v>
       </c>
       <c r="C12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D12" t="n">
         <v>1.7978</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F12" t="n">
         <v>1.8431</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H12" t="n">
         <v>2.0439</v>
       </c>
     </row>
@@ -2788,12 +3454,21 @@
         <v>1.9331</v>
       </c>
       <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="n">
         <v>1.8626</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" t="n">
         <v>1.8658</v>
       </c>
-      <c r="E13" t="n">
+      <c r="G13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" t="n">
         <v>2.0325</v>
       </c>
     </row>
@@ -2805,12 +3480,21 @@
         <v>1.9533</v>
       </c>
       <c r="C14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D14" t="n">
         <v>1.804</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F14" t="n">
         <v>1.8348</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H14" t="n">
         <v>2.0317</v>
       </c>
     </row>
@@ -2822,12 +3506,21 @@
         <v>2.0423</v>
       </c>
       <c r="C15" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" t="n">
         <v>1.8173</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" t="n">
         <v>1.8316</v>
       </c>
-      <c r="E15" t="n">
+      <c r="G15" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" t="n">
         <v>1.9836</v>
       </c>
     </row>
@@ -2839,12 +3532,21 @@
         <v>2.0658</v>
       </c>
       <c r="C16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D16" t="n">
         <v>1.7811</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F16" t="n">
         <v>1.8217</v>
       </c>
-      <c r="E16" t="n">
+      <c r="G16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H16" t="n">
         <v>1.9838</v>
       </c>
     </row>
@@ -2856,12 +3558,21 @@
         <v>2.0838</v>
       </c>
       <c r="C17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" t="n">
         <v>1.7517</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" t="n">
         <v>1.8087</v>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H17" t="n">
         <v>1.9433</v>
       </c>
     </row>
@@ -2873,12 +3584,21 @@
         <v>1.9624</v>
       </c>
       <c r="C18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D18" t="n">
         <v>1.7001</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F18" t="n">
         <v>1.7856</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H18" t="n">
         <v>1.9324</v>
       </c>
     </row>
@@ -2890,12 +3610,21 @@
         <v>1.7628</v>
       </c>
       <c r="C19" t="n">
+        <v>9</v>
+      </c>
+      <c r="D19" t="n">
         <v>1.6993</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
+        <v>9</v>
+      </c>
+      <c r="F19" t="n">
         <v>1.7559</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
+        <v>9</v>
+      </c>
+      <c r="H19" t="n">
         <v>1.9102</v>
       </c>
     </row>
@@ -2907,12 +3636,21 @@
         <v>1.8553</v>
       </c>
       <c r="C20" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D20" t="n">
         <v>1.724</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F20" t="n">
         <v>1.7962</v>
       </c>
-      <c r="E20" t="n">
+      <c r="G20" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H20" t="n">
         <v>1.9607</v>
       </c>
     </row>
@@ -2924,12 +3662,21 @@
         <v>1.7695</v>
       </c>
       <c r="C21" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" t="n">
         <v>1.834</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
         <v>1.8252</v>
       </c>
-      <c r="E21" t="n">
+      <c r="G21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" t="n">
         <v>2.0366</v>
       </c>
     </row>
@@ -2941,12 +3688,21 @@
         <v>2.0637</v>
       </c>
       <c r="C22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D22" t="n">
         <v>1.777</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F22" t="n">
         <v>1.8471</v>
       </c>
-      <c r="E22" t="n">
+      <c r="G22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H22" t="n">
         <v>2.0543</v>
       </c>
     </row>
@@ -2958,12 +3714,21 @@
         <v>1.8971</v>
       </c>
       <c r="C23" t="n">
+        <v>11</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.8002</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
+        <v>11</v>
+      </c>
+      <c r="F23" t="n">
         <v>1.819</v>
       </c>
-      <c r="E23" t="n">
+      <c r="G23" t="n">
+        <v>11</v>
+      </c>
+      <c r="H23" t="n">
         <v>1.9925</v>
       </c>
     </row>
@@ -2975,12 +3740,21 @@
         <v>2.0252</v>
       </c>
       <c r="C24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D24" t="n">
         <v>1.7851</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F24" t="n">
         <v>1.8235</v>
       </c>
-      <c r="E24" t="n">
+      <c r="G24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H24" t="n">
         <v>1.988</v>
       </c>
     </row>
@@ -2992,12 +3766,21 @@
         <v>2.04</v>
       </c>
       <c r="C25" t="n">
+        <v>12</v>
+      </c>
+      <c r="D25" t="n">
         <v>1.776</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
+        <v>12</v>
+      </c>
+      <c r="F25" t="n">
         <v>1.8178</v>
       </c>
-      <c r="E25" t="n">
+      <c r="G25" t="n">
+        <v>12</v>
+      </c>
+      <c r="H25" t="n">
         <v>1.9428</v>
       </c>
     </row>
@@ -3009,12 +3792,21 @@
         <v>2.0111</v>
       </c>
       <c r="C26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D26" t="n">
         <v>1.7457</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F26" t="n">
         <v>1.7997</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H26" t="n">
         <v>1.9507</v>
       </c>
     </row>
@@ -3026,12 +3818,21 @@
         <v>1.7817</v>
       </c>
       <c r="C27" t="n">
+        <v>13</v>
+      </c>
+      <c r="D27" t="n">
         <v>1.7334</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
+        <v>13</v>
+      </c>
+      <c r="F27" t="n">
         <v>1.7858</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
+        <v>13</v>
+      </c>
+      <c r="H27" t="n">
         <v>1.9171</v>
       </c>
     </row>
@@ -3043,12 +3844,21 @@
         <v>1.7934</v>
       </c>
       <c r="C28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D28" t="n">
         <v>1.705</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F28" t="n">
         <v>1.768</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H28" t="n">
         <v>1.9148</v>
       </c>
     </row>
@@ -3060,12 +3870,21 @@
         <v>1.9947</v>
       </c>
       <c r="C29" t="n">
+        <v>14</v>
+      </c>
+      <c r="D29" t="n">
         <v>1.7939</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
+        <v>14</v>
+      </c>
+      <c r="F29" t="n">
         <v>1.8375</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
+        <v>14</v>
+      </c>
+      <c r="H29" t="n">
         <v>1.9916</v>
       </c>
     </row>
@@ -3077,12 +3896,21 @@
         <v>2.0744</v>
       </c>
       <c r="C30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="D30" t="n">
         <v>1.839</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F30" t="n">
         <v>1.8569</v>
       </c>
-      <c r="E30" t="n">
+      <c r="G30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H30" t="n">
         <v>2.0625</v>
       </c>
     </row>
@@ -3094,12 +3922,21 @@
         <v>1.8152</v>
       </c>
       <c r="C31" t="n">
+        <v>15</v>
+      </c>
+      <c r="D31" t="n">
         <v>1.8027</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
+        <v>15</v>
+      </c>
+      <c r="F31" t="n">
         <v>1.8333</v>
       </c>
-      <c r="E31" t="n">
+      <c r="G31" t="n">
+        <v>15</v>
+      </c>
+      <c r="H31" t="n">
         <v>2.0414</v>
       </c>
     </row>
@@ -3111,12 +3948,21 @@
         <v>1.9232</v>
       </c>
       <c r="C32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D32" t="n">
         <v>1.7621</v>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F32" t="n">
         <v>1.8256</v>
       </c>
-      <c r="E32" t="n">
+      <c r="G32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H32" t="n">
         <v>2.0082</v>
       </c>
     </row>
@@ -3128,12 +3974,21 @@
         <v>1.8029</v>
       </c>
       <c r="C33" t="n">
+        <v>16</v>
+      </c>
+      <c r="D33" t="n">
         <v>1.7592</v>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
+        <v>16</v>
+      </c>
+      <c r="F33" t="n">
         <v>1.7915</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
+        <v>16</v>
+      </c>
+      <c r="H33" t="n">
         <v>1.9734</v>
       </c>
     </row>
@@ -3145,12 +4000,21 @@
         <v>1.7413</v>
       </c>
       <c r="C34" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="D34" t="n">
         <v>1.7316</v>
       </c>
-      <c r="D34" t="n">
+      <c r="E34" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F34" t="n">
         <v>1.8052</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H34" t="n">
         <v>1.9551</v>
       </c>
     </row>
@@ -3162,12 +4026,21 @@
         <v>1.8349</v>
       </c>
       <c r="C35" t="n">
+        <v>17</v>
+      </c>
+      <c r="D35" t="n">
         <v>1.7321</v>
       </c>
-      <c r="D35" t="n">
+      <c r="E35" t="n">
+        <v>17</v>
+      </c>
+      <c r="F35" t="n">
         <v>1.7748</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
+        <v>17</v>
+      </c>
+      <c r="H35" t="n">
         <v>1.9279</v>
       </c>
     </row>
@@ -3179,12 +4052,21 @@
         <v>1.8263</v>
       </c>
       <c r="C36" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D36" t="n">
         <v>1.7149</v>
       </c>
-      <c r="D36" t="n">
+      <c r="E36" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F36" t="n">
         <v>1.7834</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H36" t="n">
         <v>1.8938</v>
       </c>
     </row>
@@ -3196,12 +4078,21 @@
         <v>1.7972</v>
       </c>
       <c r="C37" t="n">
+        <v>18</v>
+      </c>
+      <c r="D37" t="n">
         <v>1.7118</v>
       </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
+        <v>18</v>
+      </c>
+      <c r="F37" t="n">
         <v>1.7743</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
+        <v>18</v>
+      </c>
+      <c r="H37" t="n">
         <v>1.9203</v>
       </c>
     </row>
@@ -3213,12 +4104,21 @@
         <v>1.8489</v>
       </c>
       <c r="C38" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D38" t="n">
         <v>1.8018</v>
       </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F38" t="n">
         <v>1.8407</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H38" t="n">
         <v>2.0321</v>
       </c>
     </row>
@@ -3230,12 +4130,21 @@
         <v>1.8896</v>
       </c>
       <c r="C39" t="n">
+        <v>19</v>
+      </c>
+      <c r="D39" t="n">
         <v>1.8794</v>
       </c>
-      <c r="D39" t="n">
+      <c r="E39" t="n">
+        <v>19</v>
+      </c>
+      <c r="F39" t="n">
         <v>1.8594</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
+        <v>19</v>
+      </c>
+      <c r="H39" t="n">
         <v>2.064</v>
       </c>
     </row>
@@ -3247,12 +4156,21 @@
         <v>1.8611</v>
       </c>
       <c r="C40" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="D40" t="n">
         <v>1.8152</v>
       </c>
-      <c r="D40" t="n">
+      <c r="E40" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F40" t="n">
         <v>1.8536</v>
       </c>
-      <c r="E40" t="n">
+      <c r="G40" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H40" t="n">
         <v>2.0293</v>
       </c>
     </row>
@@ -3264,12 +4182,21 @@
         <v>1.9425</v>
       </c>
       <c r="C41" t="n">
+        <v>20</v>
+      </c>
+      <c r="D41" t="n">
         <v>1.8005</v>
       </c>
-      <c r="D41" t="n">
+      <c r="E41" t="n">
+        <v>20</v>
+      </c>
+      <c r="F41" t="n">
         <v>1.8426</v>
       </c>
-      <c r="E41" t="n">
+      <c r="G41" t="n">
+        <v>20</v>
+      </c>
+      <c r="H41" t="n">
         <v>2.0072</v>
       </c>
     </row>
@@ -3281,12 +4208,21 @@
         <v>1.8494</v>
       </c>
       <c r="C42" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="D42" t="n">
         <v>1.7626</v>
       </c>
-      <c r="D42" t="n">
+      <c r="E42" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F42" t="n">
         <v>1.8162</v>
       </c>
-      <c r="E42" t="n">
+      <c r="G42" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H42" t="n">
         <v>1.9836</v>
       </c>
     </row>
@@ -3298,12 +4234,21 @@
         <v>1.8646</v>
       </c>
       <c r="C43" t="n">
+        <v>21</v>
+      </c>
+      <c r="D43" t="n">
         <v>1.7304</v>
       </c>
-      <c r="D43" t="n">
+      <c r="E43" t="n">
+        <v>21</v>
+      </c>
+      <c r="F43" t="n">
         <v>1.7893</v>
       </c>
-      <c r="E43" t="n">
+      <c r="G43" t="n">
+        <v>21</v>
+      </c>
+      <c r="H43" t="n">
         <v>1.9615</v>
       </c>
     </row>
@@ -3315,12 +4260,21 @@
         <v>1.7784</v>
       </c>
       <c r="C44" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D44" t="n">
         <v>1.6971</v>
       </c>
-      <c r="D44" t="n">
+      <c r="E44" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F44" t="n">
         <v>1.7778</v>
       </c>
-      <c r="E44" t="n">
+      <c r="G44" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H44" t="n">
         <v>1.921</v>
       </c>
     </row>
@@ -3332,12 +4286,21 @@
         <v>1.7633</v>
       </c>
       <c r="C45" t="n">
+        <v>22</v>
+      </c>
+      <c r="D45" t="n">
         <v>1.6649</v>
       </c>
-      <c r="D45" t="n">
+      <c r="E45" t="n">
+        <v>22</v>
+      </c>
+      <c r="F45" t="n">
         <v>1.737</v>
       </c>
-      <c r="E45" t="n">
+      <c r="G45" t="n">
+        <v>22</v>
+      </c>
+      <c r="H45" t="n">
         <v>1.9038</v>
       </c>
     </row>
@@ -3349,12 +4312,21 @@
         <v>1.7838</v>
       </c>
       <c r="C46" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D46" t="n">
         <v>1.7327</v>
       </c>
-      <c r="D46" t="n">
+      <c r="E46" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F46" t="n">
         <v>1.7898</v>
       </c>
-      <c r="E46" t="n">
+      <c r="G46" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H46" t="n">
         <v>1.929</v>
       </c>
     </row>
@@ -3366,12 +4338,21 @@
         <v>1.8914</v>
       </c>
       <c r="C47" t="n">
+        <v>23</v>
+      </c>
+      <c r="D47" t="n">
         <v>1.8081</v>
       </c>
-      <c r="D47" t="n">
+      <c r="E47" t="n">
+        <v>23</v>
+      </c>
+      <c r="F47" t="n">
         <v>1.8334</v>
       </c>
-      <c r="E47" t="n">
+      <c r="G47" t="n">
+        <v>23</v>
+      </c>
+      <c r="H47" t="n">
         <v>2.0382</v>
       </c>
     </row>
@@ -3383,12 +4364,21 @@
         <v>1.9421</v>
       </c>
       <c r="C48" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="D48" t="n">
         <v>1.8483</v>
       </c>
-      <c r="D48" t="n">
+      <c r="E48" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F48" t="n">
         <v>1.857</v>
       </c>
-      <c r="E48" t="n">
+      <c r="G48" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="H48" t="n">
         <v>2.0426</v>
       </c>
     </row>
@@ -3400,12 +4390,21 @@
         <v>1.8973</v>
       </c>
       <c r="C49" t="n">
+        <v>24</v>
+      </c>
+      <c r="D49" t="n">
         <v>1.8128</v>
       </c>
-      <c r="D49" t="n">
+      <c r="E49" t="n">
+        <v>24</v>
+      </c>
+      <c r="F49" t="n">
         <v>1.8455</v>
       </c>
-      <c r="E49" t="n">
+      <c r="G49" t="n">
+        <v>24</v>
+      </c>
+      <c r="H49" t="n">
         <v>2.0164</v>
       </c>
     </row>
@@ -3417,12 +4416,21 @@
         <v>1.935</v>
       </c>
       <c r="C50" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D50" t="n">
         <v>1.8036</v>
       </c>
-      <c r="D50" t="n">
+      <c r="E50" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F50" t="n">
         <v>1.8286</v>
       </c>
-      <c r="E50" t="n">
+      <c r="G50" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H50" t="n">
         <v>1.9906</v>
       </c>
     </row>
@@ -3434,12 +4442,21 @@
         <v>1.8752</v>
       </c>
       <c r="C51" t="n">
+        <v>25</v>
+      </c>
+      <c r="D51" t="n">
         <v>1.7886</v>
       </c>
-      <c r="D51" t="n">
+      <c r="E51" t="n">
+        <v>25</v>
+      </c>
+      <c r="F51" t="n">
         <v>1.8244</v>
       </c>
-      <c r="E51" t="n">
+      <c r="G51" t="n">
+        <v>25</v>
+      </c>
+      <c r="H51" t="n">
         <v>1.9822</v>
       </c>
     </row>
@@ -3451,12 +4468,21 @@
         <v>1.7944</v>
       </c>
       <c r="C52" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D52" t="n">
         <v>1.7544</v>
       </c>
-      <c r="D52" t="n">
+      <c r="E52" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F52" t="n">
         <v>1.8117</v>
       </c>
-      <c r="E52" t="n">
+      <c r="G52" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="H52" t="n">
         <v>1.9423</v>
       </c>
     </row>
@@ -3468,12 +4494,21 @@
         <v>1.7842</v>
       </c>
       <c r="C53" t="n">
+        <v>26</v>
+      </c>
+      <c r="D53" t="n">
         <v>1.71</v>
       </c>
-      <c r="D53" t="n">
+      <c r="E53" t="n">
+        <v>26</v>
+      </c>
+      <c r="F53" t="n">
         <v>1.7918</v>
       </c>
-      <c r="E53" t="n">
+      <c r="G53" t="n">
+        <v>26</v>
+      </c>
+      <c r="H53" t="n">
         <v>1.9356</v>
       </c>
     </row>
@@ -3485,12 +4520,21 @@
         <v>1.7765</v>
       </c>
       <c r="C54" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D54" t="n">
         <v>1.6992</v>
       </c>
-      <c r="D54" t="n">
+      <c r="E54" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F54" t="n">
         <v>1.7651</v>
       </c>
-      <c r="E54" t="n">
+      <c r="G54" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="H54" t="n">
         <v>1.9071</v>
       </c>
     </row>
@@ -3502,12 +4546,21 @@
         <v>1.8669</v>
       </c>
       <c r="C55" t="n">
+        <v>27</v>
+      </c>
+      <c r="D55" t="n">
         <v>1.7494</v>
       </c>
-      <c r="D55" t="n">
+      <c r="E55" t="n">
+        <v>27</v>
+      </c>
+      <c r="F55" t="n">
         <v>1.7993</v>
       </c>
-      <c r="E55" t="n">
+      <c r="G55" t="n">
+        <v>27</v>
+      </c>
+      <c r="H55" t="n">
         <v>1.9798</v>
       </c>
     </row>
@@ -3519,12 +4572,21 @@
         <v>1.8564</v>
       </c>
       <c r="C56" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="D56" t="n">
         <v>1.8255</v>
       </c>
-      <c r="D56" t="n">
+      <c r="E56" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F56" t="n">
         <v>1.8373</v>
       </c>
-      <c r="E56" t="n">
+      <c r="G56" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H56" t="n">
         <v>2.0438</v>
       </c>
     </row>
@@ -3536,12 +4598,21 @@
         <v>1.816</v>
       </c>
       <c r="C57" t="n">
+        <v>28</v>
+      </c>
+      <c r="D57" t="n">
         <v>1.766</v>
       </c>
-      <c r="D57" t="n">
+      <c r="E57" t="n">
+        <v>28</v>
+      </c>
+      <c r="F57" t="n">
         <v>1.8228</v>
       </c>
-      <c r="E57" t="n">
+      <c r="G57" t="n">
+        <v>28</v>
+      </c>
+      <c r="H57" t="n">
         <v>2.052</v>
       </c>
     </row>
@@ -3553,12 +4624,21 @@
         <v>1.9257</v>
       </c>
       <c r="C58" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="D58" t="n">
         <v>1.803</v>
       </c>
-      <c r="D58" t="n">
+      <c r="E58" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F58" t="n">
         <v>1.8322</v>
       </c>
-      <c r="E58" t="n">
+      <c r="G58" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="H58" t="n">
         <v>2.0002</v>
       </c>
     </row>
@@ -3570,12 +4650,21 @@
         <v>1.8409</v>
       </c>
       <c r="C59" t="n">
+        <v>29</v>
+      </c>
+      <c r="D59" t="n">
         <v>1.771</v>
       </c>
-      <c r="D59" t="n">
+      <c r="E59" t="n">
+        <v>29</v>
+      </c>
+      <c r="F59" t="n">
         <v>1.8125</v>
       </c>
-      <c r="E59" t="n">
+      <c r="G59" t="n">
+        <v>29</v>
+      </c>
+      <c r="H59" t="n">
         <v>1.9915</v>
       </c>
     </row>
@@ -3587,12 +4676,21 @@
         <v>1.8237</v>
       </c>
       <c r="C60" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="D60" t="n">
         <v>1.779</v>
       </c>
-      <c r="D60" t="n">
+      <c r="E60" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="F60" t="n">
         <v>1.8126</v>
       </c>
-      <c r="E60" t="n">
+      <c r="G60" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="H60" t="n">
         <v>1.9348</v>
       </c>
     </row>
@@ -3604,12 +4702,21 @@
         <v>1.8196</v>
       </c>
       <c r="C61" t="n">
+        <v>30</v>
+      </c>
+      <c r="D61" t="n">
         <v>1.8031</v>
       </c>
-      <c r="D61" t="n">
+      <c r="E61" t="n">
+        <v>30</v>
+      </c>
+      <c r="F61" t="n">
         <v>1.8336</v>
       </c>
-      <c r="E61" t="n">
+      <c r="G61" t="n">
+        <v>30</v>
+      </c>
+      <c r="H61" t="n">
         <v>2.0975</v>
       </c>
     </row>
@@ -3621,12 +4728,21 @@
         <v>3.3561</v>
       </c>
       <c r="C62" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="D62" t="n">
         <v>2.0994</v>
       </c>
-      <c r="D62" t="n">
+      <c r="E62" t="n">
+        <v>30.52</v>
+      </c>
+      <c r="F62" t="n">
         <v>2.7276</v>
       </c>
-      <c r="E62" t="n">
+      <c r="G62" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="H62" t="n">
         <v>3.9331</v>
       </c>
     </row>
@@ -3638,12 +4754,21 @@
         <v>3.302</v>
       </c>
       <c r="C63" t="n">
+        <v>31</v>
+      </c>
+      <c r="D63" t="n">
         <v>2.3011</v>
       </c>
-      <c r="D63" t="n">
+      <c r="E63" t="n">
+        <v>31.02</v>
+      </c>
+      <c r="F63" t="n">
         <v>3.0275</v>
       </c>
-      <c r="E63" t="n">
+      <c r="G63" t="n">
+        <v>31</v>
+      </c>
+      <c r="H63" t="n">
         <v>4.2052</v>
       </c>
     </row>
@@ -3655,12 +4780,21 @@
         <v>3.1178</v>
       </c>
       <c r="C64" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="D64" t="n">
         <v>2.2983</v>
       </c>
-      <c r="D64" t="n">
+      <c r="E64" t="n">
+        <v>31.52</v>
+      </c>
+      <c r="F64" t="n">
         <v>3.0034</v>
       </c>
-      <c r="E64" t="n">
+      <c r="G64" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="H64" t="n">
         <v>4.1181</v>
       </c>
     </row>
@@ -3672,12 +4806,21 @@
         <v>2.9975</v>
       </c>
       <c r="C65" t="n">
+        <v>32</v>
+      </c>
+      <c r="D65" t="n">
         <v>2.2871</v>
       </c>
-      <c r="D65" t="n">
+      <c r="E65" t="n">
+        <v>32.02</v>
+      </c>
+      <c r="F65" t="n">
         <v>3.0173</v>
       </c>
-      <c r="E65" t="n">
+      <c r="G65" t="n">
+        <v>32</v>
+      </c>
+      <c r="H65" t="n">
         <v>4.0365</v>
       </c>
     </row>
@@ -3689,12 +4832,21 @@
         <v>2.9143</v>
       </c>
       <c r="C66" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="D66" t="n">
         <v>2.2737</v>
       </c>
-      <c r="D66" t="n">
+      <c r="E66" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="F66" t="n">
         <v>3.0106</v>
       </c>
-      <c r="E66" t="n">
+      <c r="G66" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="H66" t="n">
         <v>3.9786</v>
       </c>
     </row>
@@ -3706,12 +4858,21 @@
         <v>2.8151</v>
       </c>
       <c r="C67" t="n">
+        <v>33</v>
+      </c>
+      <c r="D67" t="n">
         <v>2.2636</v>
       </c>
-      <c r="D67" t="n">
+      <c r="E67" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="F67" t="n">
         <v>2.987</v>
       </c>
-      <c r="E67" t="n">
+      <c r="G67" t="n">
+        <v>33</v>
+      </c>
+      <c r="H67" t="n">
         <v>3.9204</v>
       </c>
     </row>
@@ -3723,12 +4884,21 @@
         <v>2.765</v>
       </c>
       <c r="C68" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="D68" t="n">
         <v>2.2594</v>
       </c>
-      <c r="D68" t="n">
+      <c r="E68" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="F68" t="n">
         <v>2.9736</v>
       </c>
-      <c r="E68" t="n">
+      <c r="G68" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="H68" t="n">
         <v>3.885</v>
       </c>
     </row>
@@ -3740,12 +4910,21 @@
         <v>2.7096</v>
       </c>
       <c r="C69" t="n">
+        <v>34</v>
+      </c>
+      <c r="D69" t="n">
         <v>2.2459</v>
       </c>
-      <c r="D69" t="n">
+      <c r="E69" t="n">
+        <v>34.02</v>
+      </c>
+      <c r="F69" t="n">
         <v>2.9626</v>
       </c>
-      <c r="E69" t="n">
+      <c r="G69" t="n">
+        <v>34</v>
+      </c>
+      <c r="H69" t="n">
         <v>3.8439</v>
       </c>
     </row>
@@ -3757,12 +4936,21 @@
         <v>2.6669</v>
       </c>
       <c r="C70" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="D70" t="n">
         <v>2.2509</v>
       </c>
-      <c r="D70" t="n">
+      <c r="E70" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="F70" t="n">
         <v>2.9477</v>
       </c>
-      <c r="E70" t="n">
+      <c r="G70" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="H70" t="n">
         <v>3.8084</v>
       </c>
     </row>
@@ -3774,12 +4962,21 @@
         <v>2.6361</v>
       </c>
       <c r="C71" t="n">
+        <v>35</v>
+      </c>
+      <c r="D71" t="n">
         <v>2.254</v>
       </c>
-      <c r="D71" t="n">
+      <c r="E71" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="F71" t="n">
         <v>2.9339</v>
       </c>
-      <c r="E71" t="n">
+      <c r="G71" t="n">
+        <v>35</v>
+      </c>
+      <c r="H71" t="n">
         <v>3.7804</v>
       </c>
     </row>
@@ -3791,12 +4988,21 @@
         <v>2.6104</v>
       </c>
       <c r="C72" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="D72" t="n">
         <v>2.2363</v>
       </c>
-      <c r="D72" t="n">
+      <c r="E72" t="n">
+        <v>35.52</v>
+      </c>
+      <c r="F72" t="n">
         <v>2.9199</v>
       </c>
-      <c r="E72" t="n">
+      <c r="G72" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="H72" t="n">
         <v>3.7484</v>
       </c>
     </row>
@@ -3808,12 +5014,21 @@
         <v>2.5737</v>
       </c>
       <c r="C73" t="n">
+        <v>36</v>
+      </c>
+      <c r="D73" t="n">
         <v>2.2033</v>
       </c>
-      <c r="D73" t="n">
+      <c r="E73" t="n">
+        <v>36.02</v>
+      </c>
+      <c r="F73" t="n">
         <v>2.9061</v>
       </c>
-      <c r="E73" t="n">
+      <c r="G73" t="n">
+        <v>36</v>
+      </c>
+      <c r="H73" t="n">
         <v>3.7064</v>
       </c>
     </row>
@@ -3825,12 +5040,21 @@
         <v>2.5313</v>
       </c>
       <c r="C74" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="D74" t="n">
         <v>2.2032</v>
       </c>
-      <c r="D74" t="n">
+      <c r="E74" t="n">
+        <v>36.52</v>
+      </c>
+      <c r="F74" t="n">
         <v>2.8722</v>
       </c>
-      <c r="E74" t="n">
+      <c r="G74" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="H74" t="n">
         <v>3.6717</v>
       </c>
     </row>
@@ -3842,12 +5066,21 @@
         <v>2.5098</v>
       </c>
       <c r="C75" t="n">
+        <v>37</v>
+      </c>
+      <c r="D75" t="n">
         <v>2.1953</v>
       </c>
-      <c r="D75" t="n">
+      <c r="E75" t="n">
+        <v>37.02</v>
+      </c>
+      <c r="F75" t="n">
         <v>2.8736</v>
       </c>
-      <c r="E75" t="n">
+      <c r="G75" t="n">
+        <v>37</v>
+      </c>
+      <c r="H75" t="n">
         <v>3.6484</v>
       </c>
     </row>
@@ -3859,12 +5092,21 @@
         <v>2.5045</v>
       </c>
       <c r="C76" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="D76" t="n">
         <v>2.1855</v>
       </c>
-      <c r="D76" t="n">
+      <c r="E76" t="n">
+        <v>37.52</v>
+      </c>
+      <c r="F76" t="n">
         <v>2.8601</v>
       </c>
-      <c r="E76" t="n">
+      <c r="G76" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H76" t="n">
         <v>3.6148</v>
       </c>
     </row>
@@ -3876,12 +5118,21 @@
         <v>2.4913</v>
       </c>
       <c r="C77" t="n">
+        <v>38</v>
+      </c>
+      <c r="D77" t="n">
         <v>2.1823</v>
       </c>
-      <c r="D77" t="n">
+      <c r="E77" t="n">
+        <v>38.02</v>
+      </c>
+      <c r="F77" t="n">
         <v>2.8423</v>
       </c>
-      <c r="E77" t="n">
+      <c r="G77" t="n">
+        <v>38</v>
+      </c>
+      <c r="H77" t="n">
         <v>3.5859</v>
       </c>
     </row>
@@ -3893,12 +5144,21 @@
         <v>2.4948</v>
       </c>
       <c r="C78" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="D78" t="n">
         <v>2.1727</v>
       </c>
-      <c r="D78" t="n">
+      <c r="E78" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="F78" t="n">
         <v>2.8367</v>
       </c>
-      <c r="E78" t="n">
+      <c r="G78" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="H78" t="n">
         <v>3.5456</v>
       </c>
     </row>
@@ -3910,12 +5170,21 @@
         <v>2.47</v>
       </c>
       <c r="C79" t="n">
+        <v>39</v>
+      </c>
+      <c r="D79" t="n">
         <v>2.1104</v>
       </c>
-      <c r="D79" t="n">
+      <c r="E79" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="F79" t="n">
         <v>2.8382</v>
       </c>
-      <c r="E79" t="n">
+      <c r="G79" t="n">
+        <v>39</v>
+      </c>
+      <c r="H79" t="n">
         <v>3.5065</v>
       </c>
     </row>
@@ -3927,12 +5196,21 @@
         <v>2.4637</v>
       </c>
       <c r="C80" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="D80" t="n">
         <v>2.1414</v>
       </c>
-      <c r="D80" t="n">
+      <c r="E80" t="n">
+        <v>39.52</v>
+      </c>
+      <c r="F80" t="n">
         <v>2.8279</v>
       </c>
-      <c r="E80" t="n">
+      <c r="G80" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="H80" t="n">
         <v>3.4809</v>
       </c>
     </row>
@@ -3944,12 +5222,21 @@
         <v>2.4541</v>
       </c>
       <c r="C81" t="n">
+        <v>40</v>
+      </c>
+      <c r="D81" t="n">
         <v>2.1636</v>
       </c>
-      <c r="D81" t="n">
+      <c r="E81" t="n">
+        <v>40.02</v>
+      </c>
+      <c r="F81" t="n">
         <v>2.8273</v>
       </c>
-      <c r="E81" t="n">
+      <c r="G81" t="n">
+        <v>40</v>
+      </c>
+      <c r="H81" t="n">
         <v>3.4522</v>
       </c>
     </row>
@@ -3961,12 +5248,21 @@
         <v>2.4578</v>
       </c>
       <c r="C82" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="D82" t="n">
         <v>2.1631</v>
       </c>
-      <c r="D82" t="n">
+      <c r="E82" t="n">
+        <v>40.52</v>
+      </c>
+      <c r="F82" t="n">
         <v>2.8211</v>
       </c>
-      <c r="E82" t="n">
+      <c r="G82" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="H82" t="n">
         <v>3.4358</v>
       </c>
     </row>
@@ -3978,12 +5274,21 @@
         <v>2.4574</v>
       </c>
       <c r="C83" t="n">
+        <v>41</v>
+      </c>
+      <c r="D83" t="n">
         <v>2.1554</v>
       </c>
-      <c r="D83" t="n">
+      <c r="E83" t="n">
+        <v>41.02</v>
+      </c>
+      <c r="F83" t="n">
         <v>2.8089</v>
       </c>
-      <c r="E83" t="n">
+      <c r="G83" t="n">
+        <v>41</v>
+      </c>
+      <c r="H83" t="n">
         <v>3.419</v>
       </c>
     </row>
@@ -3995,12 +5300,21 @@
         <v>2.4547</v>
       </c>
       <c r="C84" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="D84" t="n">
         <v>2.1532</v>
       </c>
-      <c r="D84" t="n">
+      <c r="E84" t="n">
+        <v>41.52</v>
+      </c>
+      <c r="F84" t="n">
         <v>2.7976</v>
       </c>
-      <c r="E84" t="n">
+      <c r="G84" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="H84" t="n">
         <v>3.4024</v>
       </c>
     </row>
@@ -4012,12 +5326,21 @@
         <v>2.4392</v>
       </c>
       <c r="C85" t="n">
+        <v>42</v>
+      </c>
+      <c r="D85" t="n">
         <v>2.1383</v>
       </c>
-      <c r="D85" t="n">
+      <c r="E85" t="n">
+        <v>42.02</v>
+      </c>
+      <c r="F85" t="n">
         <v>2.7931</v>
       </c>
-      <c r="E85" t="n">
+      <c r="G85" t="n">
+        <v>42</v>
+      </c>
+      <c r="H85" t="n">
         <v>3.3844</v>
       </c>
     </row>
@@ -4029,12 +5352,21 @@
         <v>2.4316</v>
       </c>
       <c r="C86" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="D86" t="n">
         <v>2.141</v>
       </c>
-      <c r="D86" t="n">
+      <c r="E86" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="F86" t="n">
         <v>2.7843</v>
       </c>
-      <c r="E86" t="n">
+      <c r="G86" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="H86" t="n">
         <v>3.3664</v>
       </c>
     </row>
@@ -4046,12 +5378,21 @@
         <v>2.4282</v>
       </c>
       <c r="C87" t="n">
+        <v>43</v>
+      </c>
+      <c r="D87" t="n">
         <v>2.1353</v>
       </c>
-      <c r="D87" t="n">
+      <c r="E87" t="n">
+        <v>43.02</v>
+      </c>
+      <c r="F87" t="n">
         <v>2.783</v>
       </c>
-      <c r="E87" t="n">
+      <c r="G87" t="n">
+        <v>43</v>
+      </c>
+      <c r="H87" t="n">
         <v>3.3447</v>
       </c>
     </row>
@@ -4063,12 +5404,21 @@
         <v>2.4115</v>
       </c>
       <c r="C88" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="D88" t="n">
         <v>2.1356</v>
       </c>
-      <c r="D88" t="n">
+      <c r="E88" t="n">
+        <v>43.52</v>
+      </c>
+      <c r="F88" t="n">
         <v>2.7763</v>
       </c>
-      <c r="E88" t="n">
+      <c r="G88" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="H88" t="n">
         <v>3.3243</v>
       </c>
     </row>
@@ -4080,12 +5430,21 @@
         <v>2.4068</v>
       </c>
       <c r="C89" t="n">
+        <v>44</v>
+      </c>
+      <c r="D89" t="n">
         <v>2.127</v>
       </c>
-      <c r="D89" t="n">
+      <c r="E89" t="n">
+        <v>44.02</v>
+      </c>
+      <c r="F89" t="n">
         <v>2.7702</v>
       </c>
-      <c r="E89" t="n">
+      <c r="G89" t="n">
+        <v>44</v>
+      </c>
+      <c r="H89" t="n">
         <v>3.3053</v>
       </c>
     </row>
@@ -4097,12 +5456,21 @@
         <v>2.3979</v>
       </c>
       <c r="C90" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="D90" t="n">
         <v>2.1272</v>
       </c>
-      <c r="D90" t="n">
+      <c r="E90" t="n">
+        <v>44.52</v>
+      </c>
+      <c r="F90" t="n">
         <v>2.7605</v>
       </c>
-      <c r="E90" t="n">
+      <c r="G90" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="H90" t="n">
         <v>3.2804</v>
       </c>
     </row>
@@ -4118,36 +5486,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>경과(분)</t>
+          <t>iCAT-v4 시간(분)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>iCAT-v4</t>
+          <t>iCAT-v4 WAF</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>CAT-47 (최적)</t>
+          <t>CAT-47 (최적) 시간(분)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>CAT-50 (견고)</t>
+          <t>CAT-47 (최적) WAF</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>CAT-37 (기본)</t>
+          <t>CAT-50 (견고) 시간(분)</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CAT-50 (견고) WAF</t>
+        </is>
+      </c>
       <c r="G1" t="inlineStr">
+        <is>
+          <t>CAT-37 (기본) 시간(분)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>CAT-37 (기본) WAF</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>워크로드 전환 시점(분)</t>
         </is>
@@ -4161,15 +5544,24 @@
         <v>1.4801</v>
       </c>
       <c r="C2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D2" t="n">
         <v>1.34</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F2" t="n">
         <v>1.3808</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2" t="n">
         <v>1.4725</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>iCAT-v4: 15.8</t>
         </is>
@@ -4177,21 +5569,30 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="B3" t="n">
         <v>1.6337</v>
       </c>
       <c r="C3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="D3" t="n">
         <v>1.5483</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="F3" t="n">
         <v>1.5017</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H3" t="n">
         <v>1.6677</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>CAT-47 (최적): 16.9</t>
         </is>
@@ -4199,21 +5600,30 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="B4" t="n">
         <v>1.3396</v>
       </c>
       <c r="C4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="D4" t="n">
         <v>1.4408</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F4" t="n">
         <v>1.3959</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H4" t="n">
         <v>1.5352</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>CAT-50 (견고): 16.4</t>
         </is>
@@ -4221,21 +5631,30 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="B5" t="n">
         <v>1.4086</v>
       </c>
       <c r="C5" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="D5" t="n">
         <v>1.4411</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="F5" t="n">
         <v>1.4386</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H5" t="n">
         <v>1.5455</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>CAT-37 (기본): 17.0</t>
         </is>
@@ -4243,569 +5662,879 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="B6" t="n">
         <v>1.5363</v>
       </c>
       <c r="C6" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="D6" t="n">
         <v>1.4338</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="F6" t="n">
         <v>1.4049</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H6" t="n">
         <v>1.5114</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="B7" t="n">
         <v>1.354</v>
       </c>
       <c r="C7" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="D7" t="n">
         <v>1.4262</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="F7" t="n">
         <v>1.4153</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H7" t="n">
         <v>1.5332</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="B8" t="n">
         <v>1.3648</v>
       </c>
       <c r="C8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="D8" t="n">
         <v>1.423</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="F8" t="n">
         <v>1.3989</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="H8" t="n">
         <v>1.5005</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="B9" t="n">
         <v>1.4094</v>
       </c>
       <c r="C9" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="D9" t="n">
         <v>1.4205</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F9" t="n">
         <v>1.3995</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="H9" t="n">
         <v>1.487</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4.5</v>
+        <v>4.58</v>
       </c>
       <c r="B10" t="n">
         <v>1.3685</v>
       </c>
       <c r="C10" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="D10" t="n">
         <v>1.4201</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F10" t="n">
         <v>1.3974</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="H10" t="n">
         <v>1.4815</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>5.08</v>
       </c>
       <c r="B11" t="n">
         <v>1.3763</v>
       </c>
       <c r="C11" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="D11" t="n">
         <v>1.4134</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="F11" t="n">
         <v>1.3918</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H11" t="n">
         <v>1.4794</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="B12" t="n">
         <v>1.4262</v>
       </c>
       <c r="C12" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="D12" t="n">
         <v>1.4229</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="F12" t="n">
         <v>1.3899</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H12" t="n">
         <v>1.4729</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="B13" t="n">
         <v>1.3727</v>
       </c>
       <c r="C13" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="D13" t="n">
         <v>1.4193</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="F13" t="n">
         <v>1.384</v>
       </c>
-      <c r="E13" t="n">
+      <c r="G13" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="H13" t="n">
         <v>1.4945</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="B14" t="n">
         <v>1.3845</v>
       </c>
       <c r="C14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D14" t="n">
         <v>1.412</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="F14" t="n">
         <v>1.3834</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="H14" t="n">
         <v>1.4646</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>7</v>
+        <v>7.12</v>
       </c>
       <c r="B15" t="n">
         <v>1.3883</v>
       </c>
       <c r="C15" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="D15" t="n">
         <v>1.4118</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="F15" t="n">
         <v>1.3829</v>
       </c>
-      <c r="E15" t="n">
+      <c r="G15" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="H15" t="n">
         <v>1.4676</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>7.5</v>
+        <v>7.62</v>
       </c>
       <c r="B16" t="n">
         <v>1.3549</v>
       </c>
       <c r="C16" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="D16" t="n">
         <v>1.4137</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="F16" t="n">
         <v>1.3884</v>
       </c>
-      <c r="E16" t="n">
+      <c r="G16" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="H16" t="n">
         <v>1.4611</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>8</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="B17" t="n">
         <v>1.3575</v>
       </c>
       <c r="C17" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="D17" t="n">
         <v>1.3999</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="F17" t="n">
         <v>1.3871</v>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="H17" t="n">
         <v>1.4603</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>8.5</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="B18" t="n">
         <v>1.381</v>
       </c>
       <c r="C18" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="D18" t="n">
         <v>1.4042</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="F18" t="n">
         <v>1.3829</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="H18" t="n">
         <v>1.4541</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>9</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="B19" t="n">
         <v>1.32</v>
       </c>
       <c r="C19" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="D19" t="n">
         <v>1.4052</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="F19" t="n">
         <v>1.3762</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="H19" t="n">
         <v>1.454</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>9.5</v>
+        <v>9.65</v>
       </c>
       <c r="B20" t="n">
         <v>1.3744</v>
       </c>
       <c r="C20" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="D20" t="n">
         <v>1.4073</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="F20" t="n">
         <v>1.3729</v>
       </c>
-      <c r="E20" t="n">
+      <c r="G20" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="H20" t="n">
         <v>1.4533</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>10</v>
+        <v>10.17</v>
       </c>
       <c r="B21" t="n">
         <v>1.3043</v>
       </c>
       <c r="C21" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="D21" t="n">
         <v>1.4015</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F21" t="n">
         <v>1.3835</v>
       </c>
-      <c r="E21" t="n">
+      <c r="G21" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="H21" t="n">
         <v>1.4435</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>10.5</v>
+        <v>10.68</v>
       </c>
       <c r="B22" t="n">
         <v>1.3589</v>
       </c>
       <c r="C22" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="D22" t="n">
         <v>1.4066</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="F22" t="n">
         <v>1.3755</v>
       </c>
-      <c r="E22" t="n">
+      <c r="G22" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H22" t="n">
         <v>1.4523</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>11</v>
+        <v>11.18</v>
       </c>
       <c r="B23" t="n">
         <v>1.324</v>
       </c>
       <c r="C23" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.4097</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="F23" t="n">
         <v>1.3664</v>
       </c>
-      <c r="E23" t="n">
+      <c r="G23" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H23" t="n">
         <v>1.4444</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="B24" t="n">
         <v>1.319</v>
       </c>
       <c r="C24" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="D24" t="n">
         <v>1.4053</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="F24" t="n">
         <v>1.3818</v>
       </c>
-      <c r="E24" t="n">
+      <c r="G24" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="H24" t="n">
         <v>1.4438</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="B25" t="n">
         <v>1.3298</v>
       </c>
       <c r="C25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="D25" t="n">
         <v>1.4092</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="F25" t="n">
         <v>1.3778</v>
       </c>
-      <c r="E25" t="n">
+      <c r="G25" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="H25" t="n">
         <v>1.4407</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>12.5</v>
+        <v>12.72</v>
       </c>
       <c r="B26" t="n">
         <v>1.3218</v>
       </c>
       <c r="C26" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="D26" t="n">
         <v>1.4019</v>
       </c>
       <c r="E26" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.3778</v>
+      </c>
+      <c r="G26" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="H26" t="n">
         <v>1.439</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>13</v>
+        <v>13.23</v>
       </c>
       <c r="B27" t="n">
         <v>1.3243</v>
       </c>
       <c r="C27" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="D27" t="n">
         <v>1.4018</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="F27" t="n">
         <v>1.3721</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="H27" t="n">
         <v>1.4402</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>13.5</v>
+        <v>13.73</v>
       </c>
       <c r="B28" t="n">
         <v>1.323</v>
       </c>
       <c r="C28" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="D28" t="n">
         <v>1.4032</v>
+      </c>
+      <c r="E28" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.3742</v>
+      </c>
+      <c r="G28" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.4385</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>14</v>
+        <v>14.23</v>
       </c>
       <c r="B29" t="n">
         <v>1.3263</v>
       </c>
       <c r="C29" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="D29" t="n">
         <v>1.4022</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="F29" t="n">
         <v>1.3693</v>
       </c>
-      <c r="E29" t="n">
-        <v>1.4385</v>
+      <c r="G29" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.4301</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>14.5</v>
+        <v>14.75</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1.3275</v>
+      </c>
+      <c r="C30" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.4026</v>
       </c>
       <c r="E30" t="n">
-        <v>1.4301</v>
+        <v>14.77</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.3699</v>
+      </c>
+      <c r="G30" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.4297</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>15</v>
+        <v>15.27</v>
       </c>
       <c r="B31" t="n">
-        <v>1.3275</v>
+        <v>1.3453</v>
       </c>
       <c r="C31" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="D31" t="n">
         <v>1.4005</v>
       </c>
-      <c r="D31" t="n">
-        <v>1.3699</v>
-      </c>
       <c r="E31" t="n">
-        <v>1.4297</v>
+        <v>15.27</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.3667</v>
+      </c>
+      <c r="G31" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.4332</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>15.5</v>
+        <v>15.77</v>
       </c>
       <c r="B32" t="n">
-        <v>1.3453</v>
+        <v>1.3441</v>
+      </c>
+      <c r="C32" t="n">
+        <v>15.75</v>
       </c>
       <c r="D32" t="n">
-        <v>1.3667</v>
+        <v>1.4041</v>
       </c>
       <c r="E32" t="n">
-        <v>1.4332</v>
+        <v>15.78</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.3729</v>
+      </c>
+      <c r="G32" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.4301</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>16</v>
-      </c>
-      <c r="B33" t="n">
-        <v>1.3441</v>
+        <v>16.27</v>
       </c>
       <c r="C33" t="n">
-        <v>1.4041</v>
+        <v>16.28</v>
       </c>
       <c r="D33" t="n">
-        <v>1.3729</v>
+        <v>1.408</v>
       </c>
       <c r="E33" t="n">
-        <v>1.4301</v>
+        <v>16.38</v>
+      </c>
+      <c r="G33" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.4287</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>16.5</v>
+        <v>16.78</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1.2849</v>
       </c>
       <c r="C34" t="n">
-        <v>1.408</v>
+        <v>16.87</v>
       </c>
       <c r="E34" t="n">
-        <v>1.4287</v>
+        <v>16.88</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.3354</v>
+      </c>
+      <c r="G34" t="n">
+        <v>16.97</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>17</v>
+        <v>17.28</v>
       </c>
       <c r="B35" t="n">
-        <v>1.2849</v>
+        <v>1.3554</v>
+      </c>
+      <c r="C35" t="n">
+        <v>17.37</v>
       </c>
       <c r="D35" t="n">
-        <v>1.3354</v>
+        <v>1.3422</v>
+      </c>
+      <c r="E35" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.3486</v>
+      </c>
+      <c r="G35" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.4821</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>17.5</v>
+        <v>17.78</v>
       </c>
       <c r="B36" t="n">
-        <v>1.3554</v>
+        <v>1.405</v>
       </c>
       <c r="C36" t="n">
-        <v>1.3422</v>
+        <v>17.88</v>
       </c>
       <c r="D36" t="n">
-        <v>1.3486</v>
+        <v>1.4323</v>
       </c>
       <c r="E36" t="n">
-        <v>1.4821</v>
+        <v>17.9</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.4496</v>
+      </c>
+      <c r="G36" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.4075</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>18</v>
+        <v>18.3</v>
       </c>
       <c r="B37" t="n">
-        <v>1.405</v>
+        <v>1.3827</v>
       </c>
       <c r="C37" t="n">
-        <v>1.4323</v>
+        <v>18.42</v>
       </c>
       <c r="D37" t="n">
-        <v>1.4496</v>
+        <v>1.4652</v>
       </c>
       <c r="E37" t="n">
-        <v>1.4075</v>
+        <v>18.42</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.4421</v>
+      </c>
+      <c r="G37" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.4467</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>18.5</v>
+        <v>18.8</v>
       </c>
       <c r="B38" t="n">
-        <v>1.3827</v>
+        <v>1.3279</v>
       </c>
       <c r="C38" t="n">
-        <v>1.4652</v>
+        <v>18.92</v>
       </c>
       <c r="D38" t="n">
-        <v>1.4421</v>
+        <v>1.4721</v>
       </c>
       <c r="E38" t="n">
-        <v>1.4467</v>
+        <v>18.93</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.4474</v>
+      </c>
+      <c r="G38" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.4759</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>19</v>
-      </c>
-      <c r="B39" t="n">
-        <v>1.3279</v>
+        <v>19.33</v>
       </c>
       <c r="C39" t="n">
-        <v>1.4721</v>
+        <v>19.42</v>
       </c>
       <c r="D39" t="n">
-        <v>1.4474</v>
+        <v>1.4644</v>
+      </c>
+      <c r="E39" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.392</v>
+      </c>
+      <c r="G39" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.4659</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>19.5</v>
-      </c>
       <c r="C40" t="n">
-        <v>1.4644</v>
+        <v>19.97</v>
       </c>
       <c r="D40" t="n">
-        <v>1.392</v>
-      </c>
-      <c r="E40" t="n">
-        <v>1.4759</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>20</v>
-      </c>
-      <c r="C41" t="n">
         <v>1.4592</v>
-      </c>
-      <c r="E41" t="n">
-        <v>1.4659</v>
       </c>
     </row>
   </sheetData>
@@ -4820,36 +6549,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>경과(분)</t>
+          <t>iCAT-v4 시간(분)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>iCAT-v4</t>
+          <t>iCAT-v4 WAF</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>CAT-47 (최적)</t>
+          <t>CAT-47 (최적) 시간(분)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>CAT-50 (견고)</t>
+          <t>CAT-47 (최적) WAF</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>CAT-37 (기본)</t>
+          <t>CAT-50 (견고) 시간(분)</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CAT-50 (견고) WAF</t>
+        </is>
+      </c>
       <c r="G1" t="inlineStr">
+        <is>
+          <t>CAT-37 (기본) 시간(분)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>CAT-37 (기본) WAF</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>워크로드 전환 시점(분)</t>
         </is>
@@ -4863,15 +6607,24 @@
         <v>1.4135</v>
       </c>
       <c r="C2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D2" t="n">
         <v>1.2576</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F2" t="n">
         <v>1.2454</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2" t="n">
         <v>1.4202</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>iCAT-v4: 3.5</t>
         </is>
@@ -4879,21 +6632,30 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="B3" t="n">
         <v>1.952</v>
       </c>
       <c r="C3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="D3" t="n">
         <v>1.9558</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="F3" t="n">
         <v>1.8551</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
         <v>1.9625</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>CAT-47 (최적): 4.0</t>
         </is>
@@ -4901,21 +6663,30 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="B4" t="n">
         <v>1.0473</v>
       </c>
       <c r="C4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="D4" t="n">
         <v>1.0574</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F4" t="n">
         <v>1.0134</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="H4" t="n">
         <v>1.0116</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>CAT-50 (견고): 4.1</t>
         </is>
@@ -4923,18 +6694,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="C5" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="D5" t="n">
         <v>1.0205</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="F5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="H5" t="n">
         <v>1.0001</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>CAT-37 (기본): 4.1</t>
         </is>
@@ -4942,558 +6722,852 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="C6" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="D6" t="n">
         <v>1.0009</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F6" t="n">
         <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="C7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D7" t="n">
         <v>1.004</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F7" t="n">
         <v>1.0003</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="B8" t="n">
         <v>1.3455</v>
       </c>
       <c r="C8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="D8" t="n">
         <v>1.0021</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F8" t="n">
         <v>1.0095</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H8" t="n">
         <v>1.0001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="B9" t="n">
         <v>1.2272</v>
       </c>
       <c r="C9" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="D9" t="n">
         <v>1.0484</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F9" t="n">
         <v>1.432</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="H9" t="n">
         <v>1.3203</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="B10" t="n">
         <v>1.1073</v>
       </c>
       <c r="C10" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="D10" t="n">
         <v>1.4272</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F10" t="n">
         <v>1.1304</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="H10" t="n">
         <v>1.1731</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="B11" t="n">
         <v>1.109</v>
       </c>
       <c r="C11" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="D11" t="n">
         <v>1.1251</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F11" t="n">
         <v>1.1325</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="H11" t="n">
         <v>1.1714</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="B12" t="n">
         <v>1.1065</v>
       </c>
       <c r="C12" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="D12" t="n">
         <v>1.1266</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F12" t="n">
         <v>1.1301</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="H12" t="n">
         <v>1.1696</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6</v>
+        <v>6.07</v>
       </c>
       <c r="B13" t="n">
         <v>1.1074</v>
       </c>
       <c r="C13" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="D13" t="n">
         <v>1.1251</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="F13" t="n">
         <v>1.1302</v>
       </c>
-      <c r="E13" t="n">
+      <c r="G13" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="H13" t="n">
         <v>1.1705</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6.5</v>
+        <v>6.57</v>
       </c>
       <c r="B14" t="n">
         <v>1.1073</v>
       </c>
       <c r="C14" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="D14" t="n">
         <v>1.1248</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="F14" t="n">
         <v>1.1299</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="H14" t="n">
         <v>1.1701</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>7</v>
+        <v>7.07</v>
       </c>
       <c r="B15" t="n">
         <v>1.1069</v>
       </c>
       <c r="C15" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="D15" t="n">
         <v>1.1235</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="F15" t="n">
         <v>1.1304</v>
       </c>
-      <c r="E15" t="n">
+      <c r="G15" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="H15" t="n">
         <v>1.1705</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>7.5</v>
+        <v>7.57</v>
       </c>
       <c r="B16" t="n">
         <v>1.1067</v>
       </c>
       <c r="C16" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="D16" t="n">
         <v>1.1237</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="F16" t="n">
         <v>1.1298</v>
       </c>
-      <c r="E16" t="n">
+      <c r="G16" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="H16" t="n">
         <v>1.1674</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>8</v>
+        <v>8.07</v>
       </c>
       <c r="B17" t="n">
         <v>1.1079</v>
       </c>
       <c r="C17" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="D17" t="n">
         <v>1.1227</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="F17" t="n">
         <v>1.1305</v>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="H17" t="n">
         <v>1.1677</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>8.5</v>
+        <v>8.57</v>
       </c>
       <c r="B18" t="n">
         <v>1.107</v>
       </c>
       <c r="C18" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="D18" t="n">
         <v>1.1234</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="F18" t="n">
         <v>1.1295</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="H18" t="n">
         <v>1.1692</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>9</v>
+        <v>9.07</v>
       </c>
       <c r="B19" t="n">
         <v>1.1073</v>
       </c>
       <c r="C19" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="D19" t="n">
         <v>1.1229</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="F19" t="n">
         <v>1.1292</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="H19" t="n">
         <v>1.1669</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>9.5</v>
+        <v>9.57</v>
       </c>
       <c r="B20" t="n">
         <v>1.1093</v>
       </c>
       <c r="C20" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="D20" t="n">
         <v>1.1237</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="F20" t="n">
         <v>1.1267</v>
       </c>
-      <c r="E20" t="n">
+      <c r="G20" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="H20" t="n">
         <v>1.1695</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>10</v>
+        <v>10.07</v>
       </c>
       <c r="B21" t="n">
         <v>1.1008</v>
       </c>
       <c r="C21" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="D21" t="n">
         <v>1.1249</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="F21" t="n">
         <v>1.1288</v>
       </c>
-      <c r="E21" t="n">
+      <c r="G21" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="H21" t="n">
         <v>1.1696</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>10.5</v>
+        <v>10.57</v>
       </c>
       <c r="B22" t="n">
         <v>1.1066</v>
       </c>
       <c r="C22" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="D22" t="n">
         <v>1.1223</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="F22" t="n">
         <v>1.1284</v>
       </c>
-      <c r="E22" t="n">
+      <c r="G22" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="H22" t="n">
         <v>1.1717</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>11</v>
+        <v>11.07</v>
       </c>
       <c r="B23" t="n">
         <v>1.0994</v>
       </c>
       <c r="C23" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.1233</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="F23" t="n">
         <v>1.1297</v>
       </c>
-      <c r="E23" t="n">
+      <c r="G23" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="H23" t="n">
         <v>1.1706</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>11.5</v>
+        <v>11.57</v>
       </c>
       <c r="B24" t="n">
         <v>1.1001</v>
       </c>
       <c r="C24" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="D24" t="n">
         <v>1.1234</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="F24" t="n">
         <v>1.1286</v>
       </c>
-      <c r="E24" t="n">
+      <c r="G24" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="H24" t="n">
         <v>1.1699</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>12</v>
+        <v>12.07</v>
       </c>
       <c r="B25" t="n">
         <v>1.0991</v>
       </c>
       <c r="C25" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="D25" t="n">
         <v>1.1225</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="F25" t="n">
         <v>1.1267</v>
       </c>
-      <c r="E25" t="n">
+      <c r="G25" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="H25" t="n">
         <v>1.1664</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>12.5</v>
+        <v>12.57</v>
       </c>
       <c r="B26" t="n">
         <v>1.101</v>
       </c>
       <c r="C26" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="D26" t="n">
         <v>1.1229</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="F26" t="n">
         <v>1.1299</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="H26" t="n">
         <v>1.1644</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>13</v>
+        <v>13.07</v>
       </c>
       <c r="B27" t="n">
         <v>1.1003</v>
       </c>
       <c r="C27" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="D27" t="n">
         <v>1.1251</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="F27" t="n">
         <v>1.129</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="H27" t="n">
         <v>1.1627</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>13.5</v>
+        <v>13.57</v>
       </c>
       <c r="B28" t="n">
         <v>1.1001</v>
       </c>
       <c r="C28" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="D28" t="n">
         <v>1.122</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="F28" t="n">
         <v>1.1283</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="H28" t="n">
         <v>1.1641</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>14</v>
+        <v>14.07</v>
       </c>
       <c r="B29" t="n">
         <v>1.1027</v>
       </c>
       <c r="C29" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="D29" t="n">
         <v>1.1234</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="F29" t="n">
         <v>1.1287</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="H29" t="n">
         <v>1.1651</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>14.5</v>
+        <v>14.57</v>
       </c>
       <c r="B30" t="n">
         <v>1.1029</v>
       </c>
       <c r="C30" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="D30" t="n">
         <v>1.1235</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="F30" t="n">
         <v>1.1271</v>
       </c>
-      <c r="E30" t="n">
+      <c r="G30" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="H30" t="n">
         <v>1.1625</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>15</v>
+        <v>15.07</v>
       </c>
       <c r="B31" t="n">
         <v>1.0996</v>
       </c>
       <c r="C31" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="D31" t="n">
         <v>1.123</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="F31" t="n">
         <v>1.1281</v>
       </c>
-      <c r="E31" t="n">
+      <c r="G31" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="H31" t="n">
         <v>1.1654</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>15.5</v>
+        <v>15.57</v>
       </c>
       <c r="B32" t="n">
         <v>1.0996</v>
       </c>
       <c r="C32" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="D32" t="n">
         <v>1.1233</v>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="F32" t="n">
         <v>1.1282</v>
       </c>
-      <c r="E32" t="n">
+      <c r="G32" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="H32" t="n">
         <v>1.1636</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>16</v>
+        <v>16.07</v>
       </c>
       <c r="B33" t="n">
         <v>1.0991</v>
       </c>
       <c r="C33" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="D33" t="n">
         <v>1.1225</v>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
+        <v>16.13</v>
+      </c>
+      <c r="F33" t="n">
         <v>1.1283</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="H33" t="n">
         <v>1.162</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>16.5</v>
+        <v>16.72</v>
       </c>
       <c r="B34" t="n">
         <v>1.1009</v>
       </c>
       <c r="C34" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="D34" t="n">
         <v>1.1229</v>
       </c>
-      <c r="D34" t="n">
+      <c r="E34" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="F34" t="n">
         <v>1.129</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="H34" t="n">
         <v>1.1636</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>17</v>
+        <v>17.25</v>
       </c>
       <c r="B35" t="n">
         <v>1.1024</v>
       </c>
       <c r="C35" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="D35" t="n">
         <v>1.1227</v>
       </c>
-      <c r="D35" t="n">
+      <c r="E35" t="n">
+        <v>17.13</v>
+      </c>
+      <c r="F35" t="n">
         <v>1.1289</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="H35" t="n">
         <v>1.1637</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>17.5</v>
+        <v>17.78</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1.0995</v>
       </c>
       <c r="C36" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="D36" t="n">
         <v>1.1233</v>
       </c>
-      <c r="D36" t="n">
+      <c r="E36" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="F36" t="n">
         <v>1.1279</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H36" t="n">
         <v>1.1677</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>18</v>
+        <v>18.28</v>
       </c>
       <c r="B37" t="n">
         <v>1.0995</v>
       </c>
       <c r="C37" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="D37" t="n">
         <v>1.1236</v>
       </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="F37" t="n">
         <v>1.1286</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="H37" t="n">
         <v>1.1627</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="B38" t="n">
-        <v>1.0995</v>
-      </c>
       <c r="C38" t="n">
+        <v>18.58</v>
+      </c>
+      <c r="D38" t="n">
         <v>1.1236</v>
       </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="F38" t="n">
         <v>1.127</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="H38" t="n">
         <v>1.1603</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>19</v>
-      </c>
       <c r="C39" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="D39" t="n">
         <v>1.122</v>
       </c>
     </row>

--- a/figs/data/fig14_lines.xlsx
+++ b/figs/data/fig14_lines.xlsx
@@ -174,12 +174,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'OLTP→Varmail'!$A$2:$A$62</f>
+              <f>'OLTP→Varmail'!$A$2:$A$61</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'OLTP→Varmail'!$B$2:$B$62</f>
+              <f>'OLTP→Varmail'!$B$2:$B$61</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -210,12 +210,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'OLTP→Varmail'!$C$2:$C$62</f>
+              <f>'OLTP→Varmail'!$C$2:$C$61</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'OLTP→Varmail'!$D$2:$D$62</f>
+              <f>'OLTP→Varmail'!$D$2:$D$61</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -246,12 +246,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'OLTP→Varmail'!$E$2:$E$62</f>
+              <f>'OLTP→Varmail'!$E$2:$E$61</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'OLTP→Varmail'!$F$2:$F$62</f>
+              <f>'OLTP→Varmail'!$F$2:$F$61</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -282,12 +282,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'OLTP→Varmail'!$G$2:$G$62</f>
+              <f>'OLTP→Varmail'!$G$2:$G$61</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'OLTP→Varmail'!$H$2:$H$62</f>
+              <f>'OLTP→Varmail'!$H$2:$H$61</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -299,6 +299,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="31"/>
+          <min val="0"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -318,14 +320,18 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="20"/>
+        <majorUnit val="5"/>
       </valAx>
       <valAx>
         <axId val="20"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="2.5"/>
+          <min val="1.12"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -345,13 +351,14 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="0.00" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -531,6 +538,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="45"/>
+          <min val="0"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -550,14 +559,18 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="20"/>
+        <majorUnit val="5"/>
       </valAx>
       <valAx>
         <axId val="20"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="4.41"/>
+          <min val="1.45"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -577,13 +590,14 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="0.00" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -638,12 +652,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'YCSB-A→YCSB-B'!$A$2:$A$40</f>
+              <f>'YCSB-A→YCSB-B'!$A$2:$A$39</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'YCSB-A→YCSB-B'!$B$2:$B$40</f>
+              <f>'YCSB-A→YCSB-B'!$B$2:$B$39</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -674,12 +688,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'YCSB-A→YCSB-B'!$C$2:$C$40</f>
+              <f>'YCSB-A→YCSB-B'!$C$2:$C$39</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'YCSB-A→YCSB-B'!$D$2:$D$40</f>
+              <f>'YCSB-A→YCSB-B'!$D$2:$D$39</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -710,12 +724,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'YCSB-A→YCSB-B'!$E$2:$E$40</f>
+              <f>'YCSB-A→YCSB-B'!$E$2:$E$39</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'YCSB-A→YCSB-B'!$F$2:$F$40</f>
+              <f>'YCSB-A→YCSB-B'!$F$2:$F$39</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -746,12 +760,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'YCSB-A→YCSB-B'!$G$2:$G$40</f>
+              <f>'YCSB-A→YCSB-B'!$G$2:$G$39</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'YCSB-A→YCSB-B'!$H$2:$H$40</f>
+              <f>'YCSB-A→YCSB-B'!$H$2:$H$39</f>
             </numRef>
           </yVal>
           <smooth val="0"/>
@@ -763,6 +777,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="20"/>
+          <min val="0"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -782,14 +798,18 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="20"/>
+        <majorUnit val="5"/>
       </valAx>
       <valAx>
         <axId val="20"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="1.7"/>
+          <min val="1.25"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -809,13 +829,14 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="0.00" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -995,6 +1016,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="20"/>
+          <min val="0"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1014,14 +1037,18 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="20"/>
+        <majorUnit val="5"/>
       </valAx>
       <valAx>
         <axId val="20"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="2.04"/>
+          <min val="0.92"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1041,13 +1068,14 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="0.00" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1064,7 +1092,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="3960000"/>
+    <ext cx="10800000" cy="5040000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1091,7 +1119,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="3960000"/>
+    <ext cx="10800000" cy="5040000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1118,7 +1146,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="3960000"/>
+    <ext cx="10800000" cy="5040000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1145,7 +1173,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="3960000"/>
+    <ext cx="10800000" cy="5040000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1452,8 +1480,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2050,7 +2081,10 @@
         <v>1.2255</v>
       </c>
       <c r="C22" t="n">
-        <v>10.53</v>
+        <v>11.08</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.2529</v>
       </c>
       <c r="E22" t="n">
         <v>10.52</v>
@@ -2073,10 +2107,10 @@
         <v>1.2259</v>
       </c>
       <c r="C23" t="n">
-        <v>11.08</v>
+        <v>11.58</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2529</v>
+        <v>1.2528</v>
       </c>
       <c r="E23" t="n">
         <v>11.02</v>
@@ -2099,10 +2133,10 @@
         <v>1.226</v>
       </c>
       <c r="C24" t="n">
-        <v>11.58</v>
+        <v>12.1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.2528</v>
+        <v>1.2529</v>
       </c>
       <c r="E24" t="n">
         <v>11.52</v>
@@ -2125,10 +2159,10 @@
         <v>1.2334</v>
       </c>
       <c r="C25" t="n">
-        <v>12.1</v>
+        <v>12.6</v>
       </c>
       <c r="D25" t="n">
-        <v>1.2529</v>
+        <v>1.2532</v>
       </c>
       <c r="E25" t="n">
         <v>12.02</v>
@@ -2151,10 +2185,10 @@
         <v>1.2232</v>
       </c>
       <c r="C26" t="n">
-        <v>12.6</v>
+        <v>13.1</v>
       </c>
       <c r="D26" t="n">
-        <v>1.2532</v>
+        <v>1.2523</v>
       </c>
       <c r="E26" t="n">
         <v>12.52</v>
@@ -2177,10 +2211,10 @@
         <v>1.2265</v>
       </c>
       <c r="C27" t="n">
-        <v>13.1</v>
+        <v>13.6</v>
       </c>
       <c r="D27" t="n">
-        <v>1.2523</v>
+        <v>1.2525</v>
       </c>
       <c r="E27" t="n">
         <v>13.02</v>
@@ -2203,10 +2237,10 @@
         <v>1.2197</v>
       </c>
       <c r="C28" t="n">
-        <v>13.6</v>
+        <v>14.1</v>
       </c>
       <c r="D28" t="n">
-        <v>1.2525</v>
+        <v>1.2526</v>
       </c>
       <c r="E28" t="n">
         <v>13.52</v>
@@ -2229,10 +2263,10 @@
         <v>1.2197</v>
       </c>
       <c r="C29" t="n">
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="D29" t="n">
-        <v>1.2526</v>
+        <v>1.2538</v>
       </c>
       <c r="E29" t="n">
         <v>14.02</v>
@@ -2255,10 +2289,10 @@
         <v>1.2198</v>
       </c>
       <c r="C30" t="n">
-        <v>14.6</v>
+        <v>15.1</v>
       </c>
       <c r="D30" t="n">
-        <v>1.2538</v>
+        <v>1.2515</v>
       </c>
       <c r="E30" t="n">
         <v>14.52</v>
@@ -2281,10 +2315,10 @@
         <v>1.2199</v>
       </c>
       <c r="C31" t="n">
-        <v>15.1</v>
+        <v>15.6</v>
       </c>
       <c r="D31" t="n">
-        <v>1.2515</v>
+        <v>1.6821</v>
       </c>
       <c r="E31" t="n">
         <v>15.02</v>
@@ -2301,13 +2335,16 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>15.53</v>
+        <v>16.03</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1.5036</v>
       </c>
       <c r="C32" t="n">
-        <v>15.6</v>
+        <v>16.1</v>
       </c>
       <c r="D32" t="n">
-        <v>1.6821</v>
+        <v>1.9809</v>
       </c>
       <c r="E32" t="n">
         <v>15.52</v>
@@ -2324,16 +2361,16 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>16.03</v>
+        <v>16.53</v>
       </c>
       <c r="B33" t="n">
-        <v>1.5036</v>
+        <v>1.9627</v>
       </c>
       <c r="C33" t="n">
-        <v>16.1</v>
+        <v>16.6</v>
       </c>
       <c r="D33" t="n">
-        <v>1.9809</v>
+        <v>2.0074</v>
       </c>
       <c r="E33" t="n">
         <v>16.02</v>
@@ -2350,16 +2387,16 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>16.53</v>
+        <v>17.03</v>
       </c>
       <c r="B34" t="n">
-        <v>1.9627</v>
+        <v>1.9591</v>
       </c>
       <c r="C34" t="n">
-        <v>16.6</v>
+        <v>17.1</v>
       </c>
       <c r="D34" t="n">
-        <v>2.0074</v>
+        <v>2.011</v>
       </c>
       <c r="E34" t="n">
         <v>16.52</v>
@@ -2376,16 +2413,16 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>17.03</v>
+        <v>17.53</v>
       </c>
       <c r="B35" t="n">
-        <v>1.9591</v>
+        <v>1.9602</v>
       </c>
       <c r="C35" t="n">
-        <v>17.1</v>
+        <v>17.6</v>
       </c>
       <c r="D35" t="n">
-        <v>2.011</v>
+        <v>2.0183</v>
       </c>
       <c r="E35" t="n">
         <v>17.02</v>
@@ -2402,16 +2439,16 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>17.53</v>
+        <v>18.03</v>
       </c>
       <c r="B36" t="n">
-        <v>1.9602</v>
+        <v>1.9649</v>
       </c>
       <c r="C36" t="n">
-        <v>17.6</v>
+        <v>18.1</v>
       </c>
       <c r="D36" t="n">
-        <v>2.0183</v>
+        <v>2.0225</v>
       </c>
       <c r="E36" t="n">
         <v>17.52</v>
@@ -2428,16 +2465,16 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>18.03</v>
+        <v>18.53</v>
       </c>
       <c r="B37" t="n">
-        <v>1.9649</v>
+        <v>1.9705</v>
       </c>
       <c r="C37" t="n">
-        <v>18.1</v>
+        <v>18.6</v>
       </c>
       <c r="D37" t="n">
-        <v>2.0225</v>
+        <v>2.0224</v>
       </c>
       <c r="E37" t="n">
         <v>18.02</v>
@@ -2454,16 +2491,16 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>18.53</v>
+        <v>19.03</v>
       </c>
       <c r="B38" t="n">
-        <v>1.9705</v>
+        <v>1.9668</v>
       </c>
       <c r="C38" t="n">
-        <v>18.6</v>
+        <v>19.1</v>
       </c>
       <c r="D38" t="n">
-        <v>2.0224</v>
+        <v>2.0231</v>
       </c>
       <c r="E38" t="n">
         <v>18.52</v>
@@ -2480,16 +2517,16 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>19.03</v>
+        <v>19.53</v>
       </c>
       <c r="B39" t="n">
-        <v>1.9668</v>
+        <v>1.9673</v>
       </c>
       <c r="C39" t="n">
-        <v>19.1</v>
+        <v>19.6</v>
       </c>
       <c r="D39" t="n">
-        <v>2.0231</v>
+        <v>2.0256</v>
       </c>
       <c r="E39" t="n">
         <v>19.02</v>
@@ -2506,16 +2543,16 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>19.53</v>
+        <v>20.03</v>
       </c>
       <c r="B40" t="n">
-        <v>1.9673</v>
+        <v>1.9674</v>
       </c>
       <c r="C40" t="n">
-        <v>19.6</v>
+        <v>20.1</v>
       </c>
       <c r="D40" t="n">
-        <v>2.0256</v>
+        <v>2.0252</v>
       </c>
       <c r="E40" t="n">
         <v>19.52</v>
@@ -2532,16 +2569,16 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>20.03</v>
+        <v>20.53</v>
       </c>
       <c r="B41" t="n">
-        <v>1.9674</v>
+        <v>1.9679</v>
       </c>
       <c r="C41" t="n">
-        <v>20.1</v>
+        <v>20.6</v>
       </c>
       <c r="D41" t="n">
-        <v>2.0252</v>
+        <v>2.0256</v>
       </c>
       <c r="E41" t="n">
         <v>20.02</v>
@@ -2558,16 +2595,16 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>20.53</v>
+        <v>21.03</v>
       </c>
       <c r="B42" t="n">
-        <v>1.9679</v>
+        <v>1.9695</v>
       </c>
       <c r="C42" t="n">
-        <v>20.6</v>
+        <v>21.1</v>
       </c>
       <c r="D42" t="n">
-        <v>2.0256</v>
+        <v>2.0234</v>
       </c>
       <c r="E42" t="n">
         <v>20.52</v>
@@ -2584,16 +2621,16 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>21.03</v>
+        <v>21.53</v>
       </c>
       <c r="B43" t="n">
-        <v>1.9695</v>
+        <v>1.965</v>
       </c>
       <c r="C43" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="D43" t="n">
-        <v>2.0234</v>
+        <v>2.0273</v>
       </c>
       <c r="E43" t="n">
         <v>21.02</v>
@@ -2610,16 +2647,16 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>21.53</v>
+        <v>22.03</v>
       </c>
       <c r="B44" t="n">
-        <v>1.965</v>
+        <v>1.9669</v>
       </c>
       <c r="C44" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="D44" t="n">
-        <v>2.0273</v>
+        <v>2.0238</v>
       </c>
       <c r="E44" t="n">
         <v>21.52</v>
@@ -2636,16 +2673,16 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>22.03</v>
+        <v>22.53</v>
       </c>
       <c r="B45" t="n">
-        <v>1.9669</v>
+        <v>1.9661</v>
       </c>
       <c r="C45" t="n">
-        <v>22.1</v>
+        <v>22.6</v>
       </c>
       <c r="D45" t="n">
-        <v>2.0238</v>
+        <v>2.0249</v>
       </c>
       <c r="E45" t="n">
         <v>22.02</v>
@@ -2662,16 +2699,16 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>22.53</v>
+        <v>23.03</v>
       </c>
       <c r="B46" t="n">
-        <v>1.9661</v>
+        <v>1.9686</v>
       </c>
       <c r="C46" t="n">
-        <v>22.6</v>
+        <v>23.1</v>
       </c>
       <c r="D46" t="n">
-        <v>2.0249</v>
+        <v>2.0285</v>
       </c>
       <c r="E46" t="n">
         <v>22.52</v>
@@ -2688,16 +2725,16 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>23.03</v>
+        <v>23.53</v>
       </c>
       <c r="B47" t="n">
-        <v>1.9686</v>
+        <v>1.9683</v>
       </c>
       <c r="C47" t="n">
-        <v>23.1</v>
+        <v>23.6</v>
       </c>
       <c r="D47" t="n">
-        <v>2.0285</v>
+        <v>2.025</v>
       </c>
       <c r="E47" t="n">
         <v>23.02</v>
@@ -2714,16 +2751,16 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>23.53</v>
+        <v>24.03</v>
       </c>
       <c r="B48" t="n">
-        <v>1.9683</v>
+        <v>1.969</v>
       </c>
       <c r="C48" t="n">
-        <v>23.6</v>
+        <v>24.1</v>
       </c>
       <c r="D48" t="n">
-        <v>2.025</v>
+        <v>2.0243</v>
       </c>
       <c r="E48" t="n">
         <v>23.52</v>
@@ -2740,16 +2777,16 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>24.03</v>
+        <v>24.53</v>
       </c>
       <c r="B49" t="n">
-        <v>1.969</v>
+        <v>1.9731</v>
       </c>
       <c r="C49" t="n">
-        <v>24.1</v>
+        <v>24.6</v>
       </c>
       <c r="D49" t="n">
-        <v>2.0243</v>
+        <v>2.0255</v>
       </c>
       <c r="E49" t="n">
         <v>24.02</v>
@@ -2766,16 +2803,16 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>24.53</v>
+        <v>25.03</v>
       </c>
       <c r="B50" t="n">
-        <v>1.9731</v>
+        <v>1.967</v>
       </c>
       <c r="C50" t="n">
-        <v>24.6</v>
+        <v>25.1</v>
       </c>
       <c r="D50" t="n">
-        <v>2.0255</v>
+        <v>2.0265</v>
       </c>
       <c r="E50" t="n">
         <v>24.52</v>
@@ -2792,16 +2829,16 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>25.03</v>
+        <v>25.53</v>
       </c>
       <c r="B51" t="n">
-        <v>1.967</v>
+        <v>1.9673</v>
       </c>
       <c r="C51" t="n">
-        <v>25.1</v>
+        <v>25.6</v>
       </c>
       <c r="D51" t="n">
-        <v>2.0265</v>
+        <v>2.0251</v>
       </c>
       <c r="E51" t="n">
         <v>25.02</v>
@@ -2818,16 +2855,16 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>25.53</v>
+        <v>26.03</v>
       </c>
       <c r="B52" t="n">
-        <v>1.9673</v>
+        <v>1.9619</v>
       </c>
       <c r="C52" t="n">
-        <v>25.6</v>
+        <v>26.1</v>
       </c>
       <c r="D52" t="n">
-        <v>2.0251</v>
+        <v>2.0261</v>
       </c>
       <c r="E52" t="n">
         <v>25.52</v>
@@ -2844,16 +2881,16 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>26.03</v>
+        <v>26.53</v>
       </c>
       <c r="B53" t="n">
-        <v>1.9619</v>
+        <v>1.9612</v>
       </c>
       <c r="C53" t="n">
-        <v>26.1</v>
+        <v>26.6</v>
       </c>
       <c r="D53" t="n">
-        <v>2.0261</v>
+        <v>2.0244</v>
       </c>
       <c r="E53" t="n">
         <v>26.02</v>
@@ -2870,16 +2907,16 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>26.53</v>
+        <v>27.03</v>
       </c>
       <c r="B54" t="n">
-        <v>1.9612</v>
+        <v>1.9649</v>
       </c>
       <c r="C54" t="n">
-        <v>26.6</v>
+        <v>27.1</v>
       </c>
       <c r="D54" t="n">
-        <v>2.0244</v>
+        <v>2.0275</v>
       </c>
       <c r="E54" t="n">
         <v>26.52</v>
@@ -2896,16 +2933,16 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>27.03</v>
+        <v>27.53</v>
       </c>
       <c r="B55" t="n">
-        <v>1.9649</v>
+        <v>1.9664</v>
       </c>
       <c r="C55" t="n">
-        <v>27.1</v>
+        <v>27.6</v>
       </c>
       <c r="D55" t="n">
-        <v>2.0275</v>
+        <v>2.0265</v>
       </c>
       <c r="E55" t="n">
         <v>27.02</v>
@@ -2922,16 +2959,16 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>27.53</v>
+        <v>28.03</v>
       </c>
       <c r="B56" t="n">
-        <v>1.9664</v>
+        <v>1.9675</v>
       </c>
       <c r="C56" t="n">
-        <v>27.6</v>
+        <v>28.1</v>
       </c>
       <c r="D56" t="n">
-        <v>2.0265</v>
+        <v>2.026</v>
       </c>
       <c r="E56" t="n">
         <v>27.52</v>
@@ -2948,16 +2985,16 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>28.03</v>
+        <v>28.53</v>
       </c>
       <c r="B57" t="n">
-        <v>1.9675</v>
+        <v>1.9603</v>
       </c>
       <c r="C57" t="n">
-        <v>28.1</v>
+        <v>28.6</v>
       </c>
       <c r="D57" t="n">
-        <v>2.026</v>
+        <v>2.0228</v>
       </c>
       <c r="E57" t="n">
         <v>28.02</v>
@@ -2974,16 +3011,16 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>28.53</v>
+        <v>29.03</v>
       </c>
       <c r="B58" t="n">
-        <v>1.9603</v>
+        <v>1.9619</v>
       </c>
       <c r="C58" t="n">
-        <v>28.6</v>
+        <v>29.1</v>
       </c>
       <c r="D58" t="n">
-        <v>2.0228</v>
+        <v>2.0245</v>
       </c>
       <c r="E58" t="n">
         <v>28.52</v>
@@ -3000,16 +3037,16 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>29.03</v>
+        <v>29.53</v>
       </c>
       <c r="B59" t="n">
-        <v>1.9619</v>
+        <v>1.9601</v>
       </c>
       <c r="C59" t="n">
-        <v>29.1</v>
+        <v>29.6</v>
       </c>
       <c r="D59" t="n">
-        <v>2.0245</v>
+        <v>2.024</v>
       </c>
       <c r="E59" t="n">
         <v>29.02</v>
@@ -3026,16 +3063,16 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>29.53</v>
+        <v>30.03</v>
       </c>
       <c r="B60" t="n">
-        <v>1.9601</v>
+        <v>1.9615</v>
       </c>
       <c r="C60" t="n">
-        <v>29.6</v>
+        <v>30.1</v>
       </c>
       <c r="D60" t="n">
-        <v>2.024</v>
+        <v>2.026</v>
       </c>
       <c r="E60" t="n">
         <v>29.52</v>
@@ -3052,30 +3089,16 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>30.03</v>
+        <v>30.53</v>
       </c>
       <c r="B61" t="n">
-        <v>1.9615</v>
-      </c>
-      <c r="C61" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="D61" t="n">
-        <v>2.026</v>
+        <v>1.9625</v>
       </c>
       <c r="E61" t="n">
         <v>30.02</v>
       </c>
       <c r="F61" t="n">
         <v>2.0966</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>30.53</v>
-      </c>
-      <c r="B62" t="n">
-        <v>1.9625</v>
       </c>
     </row>
   </sheetData>
@@ -3092,6 +3115,9 @@
   </sheetPr>
   <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -5486,8 +5512,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -6364,7 +6393,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>16.27</v>
+        <v>16.78</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1.2849</v>
       </c>
       <c r="C33" t="n">
         <v>16.28</v>
@@ -6373,7 +6405,10 @@
         <v>1.408</v>
       </c>
       <c r="E33" t="n">
-        <v>16.38</v>
+        <v>16.88</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.3354</v>
       </c>
       <c r="G33" t="n">
         <v>16.32</v>
@@ -6384,156 +6419,133 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>16.78</v>
+        <v>17.28</v>
       </c>
       <c r="B34" t="n">
-        <v>1.2849</v>
+        <v>1.3554</v>
       </c>
       <c r="C34" t="n">
-        <v>16.87</v>
+        <v>17.37</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.3422</v>
       </c>
       <c r="E34" t="n">
-        <v>16.88</v>
+        <v>17.4</v>
       </c>
       <c r="F34" t="n">
-        <v>1.3354</v>
+        <v>1.3486</v>
       </c>
       <c r="G34" t="n">
-        <v>16.97</v>
+        <v>17.47</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.4821</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>17.28</v>
+        <v>17.78</v>
       </c>
       <c r="B35" t="n">
-        <v>1.3554</v>
+        <v>1.405</v>
       </c>
       <c r="C35" t="n">
-        <v>17.37</v>
+        <v>17.88</v>
       </c>
       <c r="D35" t="n">
-        <v>1.3422</v>
+        <v>1.4323</v>
       </c>
       <c r="E35" t="n">
-        <v>17.4</v>
+        <v>17.9</v>
       </c>
       <c r="F35" t="n">
-        <v>1.3486</v>
+        <v>1.4496</v>
       </c>
       <c r="G35" t="n">
-        <v>17.47</v>
+        <v>17.98</v>
       </c>
       <c r="H35" t="n">
-        <v>1.4821</v>
+        <v>1.4075</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>17.78</v>
+        <v>18.3</v>
       </c>
       <c r="B36" t="n">
-        <v>1.405</v>
+        <v>1.3827</v>
       </c>
       <c r="C36" t="n">
-        <v>17.88</v>
+        <v>18.42</v>
       </c>
       <c r="D36" t="n">
-        <v>1.4323</v>
+        <v>1.4652</v>
       </c>
       <c r="E36" t="n">
-        <v>17.9</v>
+        <v>18.42</v>
       </c>
       <c r="F36" t="n">
-        <v>1.4496</v>
+        <v>1.4421</v>
       </c>
       <c r="G36" t="n">
-        <v>17.98</v>
+        <v>18.68</v>
       </c>
       <c r="H36" t="n">
-        <v>1.4075</v>
+        <v>1.4467</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>18.3</v>
+        <v>18.8</v>
       </c>
       <c r="B37" t="n">
-        <v>1.3827</v>
+        <v>1.3279</v>
       </c>
       <c r="C37" t="n">
-        <v>18.42</v>
+        <v>18.92</v>
       </c>
       <c r="D37" t="n">
-        <v>1.4652</v>
+        <v>1.4721</v>
       </c>
       <c r="E37" t="n">
-        <v>18.42</v>
+        <v>18.93</v>
       </c>
       <c r="F37" t="n">
-        <v>1.4421</v>
+        <v>1.4474</v>
       </c>
       <c r="G37" t="n">
-        <v>18.68</v>
+        <v>19.27</v>
       </c>
       <c r="H37" t="n">
-        <v>1.4467</v>
+        <v>1.4759</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="B38" t="n">
-        <v>1.3279</v>
-      </c>
       <c r="C38" t="n">
-        <v>18.92</v>
+        <v>19.42</v>
       </c>
       <c r="D38" t="n">
-        <v>1.4721</v>
+        <v>1.4644</v>
       </c>
       <c r="E38" t="n">
-        <v>18.93</v>
+        <v>19.45</v>
       </c>
       <c r="F38" t="n">
-        <v>1.4474</v>
+        <v>1.392</v>
       </c>
       <c r="G38" t="n">
-        <v>19.27</v>
+        <v>19.78</v>
       </c>
       <c r="H38" t="n">
-        <v>1.4759</v>
+        <v>1.4659</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>19.33</v>
-      </c>
       <c r="C39" t="n">
-        <v>19.42</v>
+        <v>19.97</v>
       </c>
       <c r="D39" t="n">
-        <v>1.4644</v>
-      </c>
-      <c r="E39" t="n">
-        <v>19.45</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1.392</v>
-      </c>
-      <c r="G39" t="n">
-        <v>19.78</v>
-      </c>
-      <c r="H39" t="n">
-        <v>1.4659</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" t="n">
-        <v>19.97</v>
-      </c>
-      <c r="D40" t="n">
         <v>1.4592</v>
       </c>
     </row>
@@ -6551,6 +6563,9 @@
   </sheetPr>
   <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -6694,7 +6709,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2.03</v>
+        <v>3.55</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1.3455</v>
       </c>
       <c r="C5" t="n">
         <v>2.03</v>
@@ -6722,7 +6740,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2.53</v>
+        <v>4.05</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1.2272</v>
       </c>
       <c r="C6" t="n">
         <v>2.53</v>
@@ -6737,12 +6758,18 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.53</v>
+        <v>3.05</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3.05</v>
+        <v>4.55</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1.1073</v>
       </c>
       <c r="C7" t="n">
         <v>3.05</v>
@@ -6757,18 +6784,18 @@
         <v>1.0003</v>
       </c>
       <c r="G7" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>1.0001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3.55</v>
+        <v>5.05</v>
       </c>
       <c r="B8" t="n">
-        <v>1.3455</v>
+        <v>1.109</v>
       </c>
       <c r="C8" t="n">
         <v>3.55</v>
@@ -6783,18 +6810,18 @@
         <v>1.0095</v>
       </c>
       <c r="G8" t="n">
-        <v>3.55</v>
+        <v>4.07</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0001</v>
+        <v>1.3203</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4.05</v>
+        <v>5.55</v>
       </c>
       <c r="B9" t="n">
-        <v>1.2272</v>
+        <v>1.1065</v>
       </c>
       <c r="C9" t="n">
         <v>4.05</v>
@@ -6809,18 +6836,18 @@
         <v>1.432</v>
       </c>
       <c r="G9" t="n">
-        <v>4.07</v>
+        <v>4.57</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3203</v>
+        <v>1.1731</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4.55</v>
+        <v>6.07</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1073</v>
+        <v>1.1074</v>
       </c>
       <c r="C10" t="n">
         <v>4.57</v>
@@ -6835,18 +6862,18 @@
         <v>1.1304</v>
       </c>
       <c r="G10" t="n">
-        <v>4.57</v>
+        <v>5.07</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1731</v>
+        <v>1.1714</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5.05</v>
+        <v>6.57</v>
       </c>
       <c r="B11" t="n">
-        <v>1.109</v>
+        <v>1.1073</v>
       </c>
       <c r="C11" t="n">
         <v>5.07</v>
@@ -6861,18 +6888,18 @@
         <v>1.1325</v>
       </c>
       <c r="G11" t="n">
-        <v>5.07</v>
+        <v>5.57</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1714</v>
+        <v>1.1696</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5.55</v>
+        <v>7.07</v>
       </c>
       <c r="B12" t="n">
-        <v>1.1065</v>
+        <v>1.1069</v>
       </c>
       <c r="C12" t="n">
         <v>5.57</v>
@@ -6887,18 +6914,18 @@
         <v>1.1301</v>
       </c>
       <c r="G12" t="n">
-        <v>5.57</v>
+        <v>6.07</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1696</v>
+        <v>1.1705</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6.07</v>
+        <v>7.57</v>
       </c>
       <c r="B13" t="n">
-        <v>1.1074</v>
+        <v>1.1067</v>
       </c>
       <c r="C13" t="n">
         <v>6.07</v>
@@ -6913,18 +6940,18 @@
         <v>1.1302</v>
       </c>
       <c r="G13" t="n">
-        <v>6.07</v>
+        <v>6.57</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1705</v>
+        <v>1.1701</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6.57</v>
+        <v>8.07</v>
       </c>
       <c r="B14" t="n">
-        <v>1.1073</v>
+        <v>1.1079</v>
       </c>
       <c r="C14" t="n">
         <v>6.57</v>
@@ -6939,18 +6966,18 @@
         <v>1.1299</v>
       </c>
       <c r="G14" t="n">
-        <v>6.57</v>
+        <v>7.07</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1701</v>
+        <v>1.1705</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>7.07</v>
+        <v>8.57</v>
       </c>
       <c r="B15" t="n">
-        <v>1.1069</v>
+        <v>1.107</v>
       </c>
       <c r="C15" t="n">
         <v>7.07</v>
@@ -6965,18 +6992,18 @@
         <v>1.1304</v>
       </c>
       <c r="G15" t="n">
-        <v>7.07</v>
+        <v>7.58</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1705</v>
+        <v>1.1674</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>7.57</v>
+        <v>9.07</v>
       </c>
       <c r="B16" t="n">
-        <v>1.1067</v>
+        <v>1.1073</v>
       </c>
       <c r="C16" t="n">
         <v>7.57</v>
@@ -6991,18 +7018,18 @@
         <v>1.1298</v>
       </c>
       <c r="G16" t="n">
-        <v>7.58</v>
+        <v>8.08</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1674</v>
+        <v>1.1677</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>8.07</v>
+        <v>9.57</v>
       </c>
       <c r="B17" t="n">
-        <v>1.1079</v>
+        <v>1.1093</v>
       </c>
       <c r="C17" t="n">
         <v>8.07</v>
@@ -7017,18 +7044,18 @@
         <v>1.1305</v>
       </c>
       <c r="G17" t="n">
-        <v>8.08</v>
+        <v>8.58</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1677</v>
+        <v>1.1692</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>8.57</v>
+        <v>10.07</v>
       </c>
       <c r="B18" t="n">
-        <v>1.107</v>
+        <v>1.1008</v>
       </c>
       <c r="C18" t="n">
         <v>8.57</v>
@@ -7043,18 +7070,18 @@
         <v>1.1295</v>
       </c>
       <c r="G18" t="n">
-        <v>8.58</v>
+        <v>9.08</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1692</v>
+        <v>1.1669</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>9.07</v>
+        <v>10.57</v>
       </c>
       <c r="B19" t="n">
-        <v>1.1073</v>
+        <v>1.1066</v>
       </c>
       <c r="C19" t="n">
         <v>9.07</v>
@@ -7069,18 +7096,18 @@
         <v>1.1292</v>
       </c>
       <c r="G19" t="n">
-        <v>9.08</v>
+        <v>9.58</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1669</v>
+        <v>1.1695</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>9.57</v>
+        <v>11.07</v>
       </c>
       <c r="B20" t="n">
-        <v>1.1093</v>
+        <v>1.0994</v>
       </c>
       <c r="C20" t="n">
         <v>9.57</v>
@@ -7095,18 +7122,18 @@
         <v>1.1267</v>
       </c>
       <c r="G20" t="n">
-        <v>9.58</v>
+        <v>10.08</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1695</v>
+        <v>1.1696</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>10.07</v>
+        <v>11.57</v>
       </c>
       <c r="B21" t="n">
-        <v>1.1008</v>
+        <v>1.1001</v>
       </c>
       <c r="C21" t="n">
         <v>10.07</v>
@@ -7121,18 +7148,18 @@
         <v>1.1288</v>
       </c>
       <c r="G21" t="n">
-        <v>10.08</v>
+        <v>10.58</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1696</v>
+        <v>1.1717</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>10.57</v>
+        <v>12.07</v>
       </c>
       <c r="B22" t="n">
-        <v>1.1066</v>
+        <v>1.0991</v>
       </c>
       <c r="C22" t="n">
         <v>10.57</v>
@@ -7147,18 +7174,18 @@
         <v>1.1284</v>
       </c>
       <c r="G22" t="n">
-        <v>10.58</v>
+        <v>11.08</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1717</v>
+        <v>1.1706</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>11.07</v>
+        <v>12.57</v>
       </c>
       <c r="B23" t="n">
-        <v>1.0994</v>
+        <v>1.101</v>
       </c>
       <c r="C23" t="n">
         <v>11.07</v>
@@ -7173,18 +7200,18 @@
         <v>1.1297</v>
       </c>
       <c r="G23" t="n">
-        <v>11.08</v>
+        <v>11.58</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1706</v>
+        <v>1.1699</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>11.57</v>
+        <v>13.07</v>
       </c>
       <c r="B24" t="n">
-        <v>1.1001</v>
+        <v>1.1003</v>
       </c>
       <c r="C24" t="n">
         <v>11.57</v>
@@ -7199,18 +7226,18 @@
         <v>1.1286</v>
       </c>
       <c r="G24" t="n">
-        <v>11.58</v>
+        <v>12.08</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1699</v>
+        <v>1.1664</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>12.07</v>
+        <v>13.57</v>
       </c>
       <c r="B25" t="n">
-        <v>1.0991</v>
+        <v>1.1001</v>
       </c>
       <c r="C25" t="n">
         <v>12.07</v>
@@ -7225,18 +7252,18 @@
         <v>1.1267</v>
       </c>
       <c r="G25" t="n">
-        <v>12.08</v>
+        <v>12.58</v>
       </c>
       <c r="H25" t="n">
-        <v>1.1664</v>
+        <v>1.1644</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>12.57</v>
+        <v>14.07</v>
       </c>
       <c r="B26" t="n">
-        <v>1.101</v>
+        <v>1.1027</v>
       </c>
       <c r="C26" t="n">
         <v>12.58</v>
@@ -7251,18 +7278,18 @@
         <v>1.1299</v>
       </c>
       <c r="G26" t="n">
-        <v>12.58</v>
+        <v>13.08</v>
       </c>
       <c r="H26" t="n">
-        <v>1.1644</v>
+        <v>1.1627</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>13.07</v>
+        <v>14.57</v>
       </c>
       <c r="B27" t="n">
-        <v>1.1003</v>
+        <v>1.1029</v>
       </c>
       <c r="C27" t="n">
         <v>13.08</v>
@@ -7277,18 +7304,18 @@
         <v>1.129</v>
       </c>
       <c r="G27" t="n">
-        <v>13.08</v>
+        <v>13.58</v>
       </c>
       <c r="H27" t="n">
-        <v>1.1627</v>
+        <v>1.1641</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>13.57</v>
+        <v>15.07</v>
       </c>
       <c r="B28" t="n">
-        <v>1.1001</v>
+        <v>1.0996</v>
       </c>
       <c r="C28" t="n">
         <v>13.58</v>
@@ -7303,18 +7330,18 @@
         <v>1.1283</v>
       </c>
       <c r="G28" t="n">
-        <v>13.58</v>
+        <v>14.08</v>
       </c>
       <c r="H28" t="n">
-        <v>1.1641</v>
+        <v>1.1651</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>14.07</v>
+        <v>15.57</v>
       </c>
       <c r="B29" t="n">
-        <v>1.1027</v>
+        <v>1.0996</v>
       </c>
       <c r="C29" t="n">
         <v>14.08</v>
@@ -7329,18 +7356,18 @@
         <v>1.1287</v>
       </c>
       <c r="G29" t="n">
-        <v>14.08</v>
+        <v>14.58</v>
       </c>
       <c r="H29" t="n">
-        <v>1.1651</v>
+        <v>1.1625</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>14.57</v>
+        <v>16.07</v>
       </c>
       <c r="B30" t="n">
-        <v>1.1029</v>
+        <v>1.0991</v>
       </c>
       <c r="C30" t="n">
         <v>14.58</v>
@@ -7355,18 +7382,18 @@
         <v>1.1271</v>
       </c>
       <c r="G30" t="n">
-        <v>14.58</v>
+        <v>15.08</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1625</v>
+        <v>1.1654</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>15.07</v>
+        <v>16.72</v>
       </c>
       <c r="B31" t="n">
-        <v>1.0996</v>
+        <v>1.1009</v>
       </c>
       <c r="C31" t="n">
         <v>15.08</v>
@@ -7381,18 +7408,18 @@
         <v>1.1281</v>
       </c>
       <c r="G31" t="n">
-        <v>15.08</v>
+        <v>15.58</v>
       </c>
       <c r="H31" t="n">
-        <v>1.1654</v>
+        <v>1.1636</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>15.57</v>
+        <v>17.25</v>
       </c>
       <c r="B32" t="n">
-        <v>1.0996</v>
+        <v>1.1024</v>
       </c>
       <c r="C32" t="n">
         <v>15.58</v>
@@ -7407,18 +7434,18 @@
         <v>1.1282</v>
       </c>
       <c r="G32" t="n">
-        <v>15.58</v>
+        <v>16.08</v>
       </c>
       <c r="H32" t="n">
-        <v>1.1636</v>
+        <v>1.162</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>16.07</v>
+        <v>17.78</v>
       </c>
       <c r="B33" t="n">
-        <v>1.0991</v>
+        <v>1.0995</v>
       </c>
       <c r="C33" t="n">
         <v>16.08</v>
@@ -7433,18 +7460,18 @@
         <v>1.1283</v>
       </c>
       <c r="G33" t="n">
-        <v>16.08</v>
+        <v>16.58</v>
       </c>
       <c r="H33" t="n">
-        <v>1.162</v>
+        <v>1.1636</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>16.72</v>
+        <v>18.28</v>
       </c>
       <c r="B34" t="n">
-        <v>1.1009</v>
+        <v>1.0995</v>
       </c>
       <c r="C34" t="n">
         <v>16.58</v>
@@ -7459,19 +7486,13 @@
         <v>1.129</v>
       </c>
       <c r="G34" t="n">
-        <v>16.58</v>
+        <v>17.08</v>
       </c>
       <c r="H34" t="n">
-        <v>1.1636</v>
+        <v>1.1637</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>17.25</v>
-      </c>
-      <c r="B35" t="n">
-        <v>1.1024</v>
-      </c>
       <c r="C35" t="n">
         <v>17.08</v>
       </c>
@@ -7485,19 +7506,13 @@
         <v>1.1289</v>
       </c>
       <c r="G35" t="n">
-        <v>17.08</v>
+        <v>17.6</v>
       </c>
       <c r="H35" t="n">
-        <v>1.1637</v>
+        <v>1.1677</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>17.78</v>
-      </c>
-      <c r="B36" t="n">
-        <v>1.0995</v>
-      </c>
       <c r="C36" t="n">
         <v>17.58</v>
       </c>
@@ -7511,19 +7526,13 @@
         <v>1.1279</v>
       </c>
       <c r="G36" t="n">
-        <v>17.6</v>
+        <v>18.12</v>
       </c>
       <c r="H36" t="n">
-        <v>1.1677</v>
+        <v>1.1627</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>18.28</v>
-      </c>
-      <c r="B37" t="n">
-        <v>1.0995</v>
-      </c>
       <c r="C37" t="n">
         <v>18.08</v>
       </c>
@@ -7537,10 +7546,10 @@
         <v>1.1286</v>
       </c>
       <c r="G37" t="n">
-        <v>18.12</v>
+        <v>18.63</v>
       </c>
       <c r="H37" t="n">
-        <v>1.1627</v>
+        <v>1.1603</v>
       </c>
     </row>
     <row r="38">
@@ -7555,12 +7564,6 @@
       </c>
       <c r="F38" t="n">
         <v>1.127</v>
-      </c>
-      <c r="G38" t="n">
-        <v>18.63</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1.1603</v>
       </c>
     </row>
     <row r="39">

--- a/figs/data/fig14_lines.xlsx
+++ b/figs/data/fig14_lines.xlsx
@@ -148,6 +148,7 @@
     </title>
     <plotArea>
       <scatterChart>
+        <scatterStyle val="lineMarker"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
@@ -361,7 +362,7 @@
       <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
+    <dispBlanksAs val="span"/>
   </chart>
 </chartSpace>
 </file>
@@ -387,6 +388,7 @@
     </title>
     <plotArea>
       <scatterChart>
+        <scatterStyle val="lineMarker"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
@@ -600,7 +602,7 @@
       <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
+    <dispBlanksAs val="span"/>
   </chart>
 </chartSpace>
 </file>
@@ -626,6 +628,7 @@
     </title>
     <plotArea>
       <scatterChart>
+        <scatterStyle val="lineMarker"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
@@ -839,7 +842,7 @@
       <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
+    <dispBlanksAs val="span"/>
   </chart>
 </chartSpace>
 </file>
@@ -865,6 +868,7 @@
     </title>
     <plotArea>
       <scatterChart>
+        <scatterStyle val="lineMarker"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
@@ -1078,7 +1082,7 @@
       <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
+    <dispBlanksAs val="span"/>
   </chart>
 </chartSpace>
 </file>

--- a/figs/data/fig14_lines.xlsx
+++ b/figs/data/fig14_lines.xlsx
@@ -293,6 +293,41 @@
           </yVal>
           <smooth val="0"/>
         </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'OLTP→Varmail'!L1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="E5484D"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'OLTP→Varmail'!$K$2:$K$3</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'OLTP→Varmail'!$L$2:$L$3</f>
+            </numRef>
+          </yVal>
+        </ser>
         <axId val="10"/>
         <axId val="20"/>
       </scatterChart>
@@ -532,6 +567,41 @@
             </numRef>
           </yVal>
           <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'FIO-Fast→Varmail'!L1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="E5484D"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'FIO-Fast→Varmail'!$K$2:$K$3</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'FIO-Fast→Varmail'!$L$2:$L$3</f>
+            </numRef>
+          </yVal>
         </ser>
         <axId val="10"/>
         <axId val="20"/>
@@ -773,6 +843,41 @@
           </yVal>
           <smooth val="0"/>
         </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'YCSB-A→YCSB-B'!L1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="E5484D"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'YCSB-A→YCSB-B'!$K$2:$K$3</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'YCSB-A→YCSB-B'!$L$2:$L$3</f>
+            </numRef>
+          </yVal>
+        </ser>
         <axId val="10"/>
         <axId val="20"/>
       </scatterChart>
@@ -1013,6 +1118,41 @@
           </yVal>
           <smooth val="0"/>
         </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'YCSB-A→OLTP'!L1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="E5484D"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'YCSB-A→OLTP'!$K$2:$K$3</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'YCSB-A→OLTP'!$L$2:$L$3</f>
+            </numRef>
+          </yVal>
+        </ser>
         <axId val="10"/>
         <axId val="20"/>
       </scatterChart>
@@ -1091,7 +1231,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>13</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1118,7 +1258,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>13</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1145,7 +1285,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>13</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1172,7 +1312,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>13</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1484,7 +1624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="10" max="10"/>
@@ -1536,6 +1676,16 @@
           <t>워크로드 전환 시점(분)</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>전환 시간</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>워크로드 전환 (v4 기준 16.0분)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1567,6 +1717,12 @@
           <t>iCAT-v4: 16.0</t>
         </is>
       </c>
+      <c r="K2" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.12</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1597,6 +1753,12 @@
         <is>
           <t>CAT-47 (최적): 15.6</t>
         </is>
+      </c>
+      <c r="K3" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
@@ -3117,7 +3279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:L90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="10" max="10"/>
@@ -3169,6 +3331,16 @@
           <t>워크로드 전환 시점(분)</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>전환 시간</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>워크로드 전환 (v4 기준 30.0분)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -3200,6 +3372,12 @@
           <t>iCAT-v4: 30.0</t>
         </is>
       </c>
+      <c r="K2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -3230,6 +3408,12 @@
         <is>
           <t>CAT-47 (최적): 30.0</t>
         </is>
+      </c>
+      <c r="K3" t="n">
+        <v>30</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4.41</v>
       </c>
     </row>
     <row r="4">
@@ -5516,7 +5700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="10" max="10"/>
@@ -5568,6 +5752,16 @@
           <t>워크로드 전환 시점(분)</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>전환 시간</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>워크로드 전환 (v4 기준 15.8분)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -5599,6 +5793,12 @@
           <t>iCAT-v4: 15.8</t>
         </is>
       </c>
+      <c r="K2" t="n">
+        <v>15.77</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.25</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -5629,6 +5829,12 @@
         <is>
           <t>CAT-47 (최적): 16.9</t>
         </is>
+      </c>
+      <c r="K3" t="n">
+        <v>15.77</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="4">
@@ -6565,7 +6771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="10" max="10"/>
@@ -6617,6 +6823,16 @@
           <t>워크로드 전환 시점(분)</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>전환 시간</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>워크로드 전환 (v4 기준 3.5분)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -6648,6 +6864,12 @@
           <t>iCAT-v4: 3.5</t>
         </is>
       </c>
+      <c r="K2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.92</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -6678,6 +6900,12 @@
         <is>
           <t>CAT-47 (최적): 4.0</t>
         </is>
+      </c>
+      <c r="K3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.04</v>
       </c>
     </row>
     <row r="4">
